--- a/testing/reports/Master_E2E_Analysis_Report.xlsx
+++ b/testing/reports/Master_E2E_Analysis_Report.xlsx
@@ -26,7 +26,7 @@
     <t>Execution Date &amp; Timestamp</t>
   </si>
   <si>
-    <t>8/4/2026, 7:45:44 PM</t>
+    <t>8/4/2026, 8:03:42 PM</t>
   </si>
   <si>
     <t>Total Unique Test Cases Executed</t>
@@ -47,7 +47,7 @@
     <t>Total Execution Duration</t>
   </si>
   <si>
-    <t>30.84 seconds</t>
+    <t>15.88 seconds</t>
   </si>
   <si>
     <t>--- CATEGORY BREAKDOWN ---</t>
@@ -125,7 +125,7 @@
     <t>PASS</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:19.999Z</t>
+    <t>2026-08-04T14:33:33.642Z</t>
   </si>
   <si>
     <t/>
@@ -137,7 +137,7 @@
     <t>Verify head tilt angle normalization algorithm (-90 to +90 degrees)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:20.026Z</t>
+    <t>2026-08-04T14:33:33.687Z</t>
   </si>
   <si>
     <t>TC-UNIT-003</t>
@@ -146,7 +146,7 @@
     <t>Verify spine alignment vector dot product score calculation</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:20.043Z</t>
+    <t>2026-08-04T14:33:33.707Z</t>
   </si>
   <si>
     <t>TC-UNIT-004</t>
@@ -155,7 +155,7 @@
     <t>Verify eye contact stability variance index parser</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:20.076Z</t>
+    <t>2026-08-04T14:33:33.734Z</t>
   </si>
   <si>
     <t>TC-UNIT-005</t>
@@ -164,7 +164,7 @@
     <t>Verify gesture frequency counter moving average window (5 sec frame window)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:20.092Z</t>
+    <t>2026-08-04T14:33:33.756Z</t>
   </si>
   <si>
     <t>TC-UNIT-006</t>
@@ -173,7 +173,7 @@
     <t>Verify audio pitch detection autocorrelation frequency extraction (80Hz - 400Hz)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:20.109Z</t>
+    <t>2026-08-04T14:33:33.785Z</t>
   </si>
   <si>
     <t>TC-UNIT-007</t>
@@ -182,7 +182,7 @@
     <t>Verify speech rate WPM (Words Per Minute) calculation from audio buffer</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:20.126Z</t>
+    <t>2026-08-04T14:33:33.803Z</t>
   </si>
   <si>
     <t>TC-UNIT-008</t>
@@ -191,7 +191,7 @@
     <t>Verify pause duration frequency histogram generator</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:20.142Z</t>
+    <t>2026-08-04T14:33:33.824Z</t>
   </si>
   <si>
     <t>TC-UNIT-009</t>
@@ -200,7 +200,7 @@
     <t>Verify overall presentation score weighted aggregator (Posture + Audio)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:20.159Z</t>
+    <t>2026-08-04T14:33:33.857Z</t>
   </si>
   <si>
     <t>TC-UNIT-010</t>
@@ -209,7 +209,7 @@
     <t>Verify session streak counter consecutive day calculation logic</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:20.175Z</t>
+    <t>2026-08-04T14:33:33.874Z</t>
   </si>
   <si>
     <t>TC-UNIT-011</t>
@@ -218,7 +218,7 @@
     <t>Verify streak reset when missing 48 hour window</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:20.192Z</t>
+    <t>2026-08-04T14:33:33.897Z</t>
   </si>
   <si>
     <t>TC-UNIT-012</t>
@@ -227,7 +227,7 @@
     <t>Verify date formatting helper for ISO 8601 timestamps</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:20.209Z</t>
+    <t>2026-08-04T14:33:33.913Z</t>
   </si>
   <si>
     <t>TC-UNIT-013</t>
@@ -236,7 +236,7 @@
     <t>Verify Session history JSON serializer object parser</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:20.224Z</t>
+    <t>2026-08-04T14:33:33.940Z</t>
   </si>
   <si>
     <t>TC-UNIT-014</t>
@@ -245,7 +245,7 @@
     <t>Verify Session history deserialization from local storage JSON string</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:20.240Z</t>
+    <t>2026-08-04T14:33:33.955Z</t>
   </si>
   <si>
     <t>TC-UNIT-015</t>
@@ -254,7 +254,7 @@
     <t>Verify SharedPreferences state key-value data mapper</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:20.257Z</t>
+    <t>2026-08-04T14:33:33.971Z</t>
   </si>
   <si>
     <t>TC-UNIT-016</t>
@@ -263,7 +263,7 @@
     <t>Verify posture feedback recommendation text selector based on score threshold</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:20.276Z</t>
+    <t>2026-08-04T14:33:33.991Z</t>
   </si>
   <si>
     <t>TC-UNIT-017</t>
@@ -272,7 +272,7 @@
     <t>Verify shoulder asymmetry threshold detection (&gt;15px delta)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:20.307Z</t>
+    <t>2026-08-04T14:33:34.010Z</t>
   </si>
   <si>
     <t>TC-UNIT-018</t>
@@ -281,7 +281,7 @@
     <t>Verify slouching body inclination angle calculation (&gt;20 deg forward)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:20.323Z</t>
+    <t>2026-08-04T14:33:34.041Z</t>
   </si>
   <si>
     <t>TC-UNIT-019</t>
@@ -290,7 +290,7 @@
     <t>Verify fidgeting movement jitter RMS (Root Mean Square) metric calculation</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:20.339Z</t>
+    <t>2026-08-04T14:33:34.057Z</t>
   </si>
   <si>
     <t>TC-UNIT-020</t>
@@ -299,7 +299,7 @@
     <t>Verify facial landmark distance ratio calculation for smile detection</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:20.354Z</t>
+    <t>2026-08-04T14:33:34.079Z</t>
   </si>
   <si>
     <t>TC-UNIT-021</t>
@@ -308,7 +308,7 @@
     <t>Verify blink rate per minute estimation algorithm from eye aspect ratio (EAR)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:20.376Z</t>
+    <t>2026-08-04T14:33:34.104Z</t>
   </si>
   <si>
     <t>TC-UNIT-022</t>
@@ -317,7 +317,7 @@
     <t>Verify gaze direction vector mapping (Left, Right, Center, Up, Down)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:20.392Z</t>
+    <t>2026-08-04T14:33:34.120Z</t>
   </si>
   <si>
     <t>TC-UNIT-023</t>
@@ -326,7 +326,7 @@
     <t>Verify voice volume dB level peak normalization transformer</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:20.409Z</t>
+    <t>2026-08-04T14:33:34.144Z</t>
   </si>
   <si>
     <t>TC-UNIT-024</t>
@@ -335,7 +335,7 @@
     <t>Verify vocal clarity spectral centroid calculation helper</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:20.426Z</t>
+    <t>2026-08-04T14:33:34.173Z</t>
   </si>
   <si>
     <t>TC-UNIT-025</t>
@@ -344,7 +344,7 @@
     <t>Verify filler word counter regex pattern matcher ("um", "uh", "like")</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:20.457Z</t>
+    <t>2026-08-04T14:33:34.203Z</t>
   </si>
   <si>
     <t>TC-UNIT-026</t>
@@ -353,7 +353,7 @@
     <t>Verify Session timer duration elapsed string formatter (MM:SS)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:20.481Z</t>
+    <t>2026-08-04T14:33:34.227Z</t>
   </si>
   <si>
     <t>TC-UNIT-027</t>
@@ -362,7 +362,7 @@
     <t>Verify user progress score percentile rank calculation</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:20.496Z</t>
+    <t>2026-08-04T14:33:34.254Z</t>
   </si>
   <si>
     <t>TC-UNIT-028</t>
@@ -371,7 +371,7 @@
     <t>Verify badge achievement unlock checker logic (3-day streak badge)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:20.519Z</t>
+    <t>2026-08-04T14:33:34.274Z</t>
   </si>
   <si>
     <t>TC-UNIT-029</t>
@@ -380,7 +380,7 @@
     <t>Verify CSV exporter string formatter row generator</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:20.536Z</t>
+    <t>2026-08-04T14:33:34.290Z</t>
   </si>
   <si>
     <t>TC-UNIT-030</t>
@@ -389,7 +389,7 @@
     <t>Verify PDF report document page margin and header layout builder</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:20.561Z</t>
+    <t>2026-08-04T14:33:34.307Z</t>
   </si>
   <si>
     <t>TC-UNIT-031</t>
@@ -398,7 +398,7 @@
     <t>Verify color hex string to HSL color space converter</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:20.587Z</t>
+    <t>2026-08-04T14:33:34.324Z</t>
   </si>
   <si>
     <t>TC-UNIT-032</t>
@@ -407,7 +407,7 @@
     <t>Verify dark theme color palette contrast calculation helper</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:20.603Z</t>
+    <t>2026-08-04T14:33:34.341Z</t>
   </si>
   <si>
     <t>TC-UNIT-033</t>
@@ -416,7 +416,7 @@
     <t>Verify dynamic chart dataset data point interpolation helper</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:20.618Z</t>
+    <t>2026-08-04T14:33:34.357Z</t>
   </si>
   <si>
     <t>TC-UNIT-034</t>
@@ -425,7 +425,7 @@
     <t>Verify bounding box intersection over union (IoU) calculation</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:20.637Z</t>
+    <t>2026-08-04T14:33:34.390Z</t>
   </si>
   <si>
     <t>TC-UNIT-035</t>
@@ -434,7 +434,7 @@
     <t>Verify camera frame cropping transform matrix calculator</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:20.653Z</t>
+    <t>2026-08-04T14:33:34.407Z</t>
   </si>
   <si>
     <t>TC-UNIT-036</t>
@@ -443,7 +443,7 @@
     <t>Verify image resolution downscaling aspect ratio resizer</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:20.668Z</t>
+    <t>2026-08-04T14:33:34.423Z</t>
   </si>
   <si>
     <t>TC-UNIT-037</t>
@@ -452,7 +452,7 @@
     <t>Verify FPS calculation rolling window queue buffer (30 frames)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:20.692Z</t>
+    <t>2026-08-04T14:33:34.440Z</t>
   </si>
   <si>
     <t>TC-UNIT-038</t>
@@ -461,7 +461,7 @@
     <t>Verify network retry exponential backoff interval algorithm</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:20.708Z</t>
+    <t>2026-08-04T14:33:34.459Z</t>
   </si>
   <si>
     <t>TC-UNIT-039</t>
@@ -470,7 +470,7 @@
     <t>Verify auth user token JWT payload decoder helper</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:20.723Z</t>
+    <t>2026-08-04T14:33:34.490Z</t>
   </si>
   <si>
     <t>TC-UNIT-040</t>
@@ -479,7 +479,7 @@
     <t>Verify local session storage key sanitization function</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:20.756Z</t>
+    <t>2026-08-04T14:33:34.523Z</t>
   </si>
   <si>
     <t>TC-UNIT-041</t>
@@ -488,7 +488,7 @@
     <t>Verify posture historical score trend slope linear regression algorithm</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:20.774Z</t>
+    <t>2026-08-04T14:33:34.540Z</t>
   </si>
   <si>
     <t>TC-UNIT-042</t>
@@ -497,7 +497,7 @@
     <t>Verify head posture status string encoder (Optimal, Mild Tilt, Severe Tilt)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:20.792Z</t>
+    <t>2026-08-04T14:33:34.557Z</t>
   </si>
   <si>
     <t>TC-UNIT-043</t>
@@ -506,7 +506,7 @@
     <t>Verify gesture expressiveness score scaling factor (0.0 - 1.0)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:20.808Z</t>
+    <t>2026-08-04T14:33:34.572Z</t>
   </si>
   <si>
     <t>TC-UNIT-044</t>
@@ -515,7 +515,7 @@
     <t>Verify voice monotone index standard deviation calculation</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:20.826Z</t>
+    <t>2026-08-04T14:33:34.590Z</t>
   </si>
   <si>
     <t>TC-UNIT-045</t>
@@ -524,7 +524,7 @@
     <t>Verify audio noise floor threshold subtraction filter</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:20.859Z</t>
+    <t>2026-08-04T14:33:34.607Z</t>
   </si>
   <si>
     <t>TC-UNIT-046</t>
@@ -533,7 +533,7 @@
     <t>Verify user profile completion percentage score calculator</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:20.875Z</t>
+    <t>2026-08-04T14:33:34.623Z</t>
   </si>
   <si>
     <t>TC-UNIT-047</t>
@@ -542,7 +542,7 @@
     <t>Verify session summary score comparison delta calculation (+/- %)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:20.909Z</t>
+    <t>2026-08-04T14:33:34.640Z</t>
   </si>
   <si>
     <t>TC-UNIT-048</t>
@@ -551,7 +551,7 @@
     <t>Verify calendar date month grid days array generator</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:20.927Z</t>
+    <t>2026-08-04T14:33:34.659Z</t>
   </si>
   <si>
     <t>TC-UNIT-049</t>
@@ -560,7 +560,7 @@
     <t>Verify email mask utility for privacy display (j***@domain.com)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:20.959Z</t>
+    <t>2026-08-04T14:33:34.690Z</t>
   </si>
   <si>
     <t>TC-UNIT-050</t>
@@ -569,7 +569,7 @@
     <t>Verify app configuration default settings fallback object builder</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:21.009Z</t>
+    <t>2026-08-04T14:33:34.707Z</t>
   </si>
   <si>
     <t>TC-FUNC-001</t>
@@ -584,7 +584,7 @@
     <t>Verify ConfidAI Web Landing Page load and header rendering</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:38.259Z</t>
+    <t>2026-08-04T14:33:36.473Z</t>
   </si>
   <si>
     <t>TC-FUNC-002</t>
@@ -593,7 +593,7 @@
     <t>Verify Login screen email text input field acceptance</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:38.289Z</t>
+    <t>2026-08-04T14:33:36.496Z</t>
   </si>
   <si>
     <t>TC-FUNC-003</t>
@@ -602,7 +602,7 @@
     <t>Verify Login screen password text input field acceptance</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:38.320Z</t>
+    <t>2026-08-04T14:33:36.523Z</t>
   </si>
   <si>
     <t>TC-FUNC-004</t>
@@ -611,7 +611,7 @@
     <t>Verify Valid Credentials Sign-In submission payload dispatch</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:38.351Z</t>
+    <t>2026-08-04T14:33:36.557Z</t>
   </si>
   <si>
     <t>TC-FUNC-005</t>
@@ -620,7 +620,7 @@
     <t>Verify Login to Register tab switch interaction</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:38.571Z</t>
+    <t>2026-08-04T14:33:36.590Z</t>
   </si>
   <si>
     <t>TC-FUNC-006</t>
@@ -629,7 +629,7 @@
     <t>Verify Register screen Full Name input field</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:38.599Z</t>
+    <t>2026-08-04T14:33:36.623Z</t>
   </si>
   <si>
     <t>TC-FUNC-007</t>
@@ -638,7 +638,7 @@
     <t>Verify Register screen Phone Number input field</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:38.624Z</t>
+    <t>2026-08-04T14:33:36.657Z</t>
   </si>
   <si>
     <t>TC-FUNC-008</t>
@@ -647,7 +647,7 @@
     <t>Verify Forgot Password link routing action</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:38.647Z</t>
+    <t>2026-08-04T14:33:36.690Z</t>
   </si>
   <si>
     <t>TC-FUNC-009</t>
@@ -656,7 +656,7 @@
     <t>Verify Password recovery email dispatch trigger</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:38.674Z</t>
+    <t>2026-08-04T14:33:36.723Z</t>
   </si>
   <si>
     <t>TC-FUNC-010</t>
@@ -665,7 +665,7 @@
     <t>Verify OTP 6-digit pin code entry and submission</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:38.701Z</t>
+    <t>2026-08-04T14:33:36.757Z</t>
   </si>
   <si>
     <t>TC-FUNC-011</t>
@@ -674,7 +674,7 @@
     <t>Verify Onboarding screen slide 1 rendering and title text</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:38.724Z</t>
+    <t>2026-08-04T14:33:36.788Z</t>
   </si>
   <si>
     <t>TC-FUNC-012</t>
@@ -683,7 +683,7 @@
     <t>Verify Onboarding slide 2 next swipe navigation</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:38.758Z</t>
+    <t>2026-08-04T14:33:36.823Z</t>
   </si>
   <si>
     <t>TC-FUNC-013</t>
@@ -692,7 +692,7 @@
     <t>Verify Onboarding slide 3 posture tips presentation</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:38.791Z</t>
+    <t>2026-08-04T14:33:36.857Z</t>
   </si>
   <si>
     <t>TC-FUNC-014</t>
@@ -701,7 +701,7 @@
     <t>Verify Onboarding Skip button navigation to Home Screen</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:38.823Z</t>
+    <t>2026-08-04T14:33:36.890Z</t>
   </si>
   <si>
     <t>TC-FUNC-015</t>
@@ -710,7 +710,7 @@
     <t>Verify Onboarding Get Started button completion flow</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:38.857Z</t>
+    <t>2026-08-04T14:33:36.923Z</t>
   </si>
   <si>
     <t>TC-FUNC-016</t>
@@ -719,7 +719,7 @@
     <t>Verify persistent login session token restoration on browser reload</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:38.888Z</t>
+    <t>2026-08-04T14:33:36.956Z</t>
   </si>
   <si>
     <t>TC-FUNC-017</t>
@@ -728,7 +728,7 @@
     <t>Verify User Logout button clearing session state</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:38.919Z</t>
+    <t>2026-08-04T14:33:36.989Z</t>
   </si>
   <si>
     <t>TC-FUNC-018</t>
@@ -737,7 +737,7 @@
     <t>Verify Navigation Drawer menu expand toggle</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:38.949Z</t>
+    <t>2026-08-04T14:33:37.021Z</t>
   </si>
   <si>
     <t>TC-FUNC-019</t>
@@ -746,7 +746,7 @@
     <t>Verify Navigation Drawer Home item click action</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:38.973Z</t>
+    <t>2026-08-04T14:33:37.057Z</t>
   </si>
   <si>
     <t>TC-FUNC-020</t>
@@ -755,7 +755,7 @@
     <t>Verify Navigation Drawer History item click action</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:38.996Z</t>
+    <t>2026-08-04T14:33:37.089Z</t>
   </si>
   <si>
     <t>TC-FUNC-021</t>
@@ -764,7 +764,7 @@
     <t>Verify Navigation Drawer Profile item click action</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:39.024Z</t>
+    <t>2026-08-04T14:33:37.123Z</t>
   </si>
   <si>
     <t>TC-FUNC-022</t>
@@ -773,7 +773,7 @@
     <t>Verify Navigation Drawer Settings item click action</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:39.047Z</t>
+    <t>2026-08-04T14:33:37.157Z</t>
   </si>
   <si>
     <t>TC-FUNC-023</t>
@@ -782,7 +782,7 @@
     <t>Verify Navigation Drawer Notifications item click action</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:39.077Z</t>
+    <t>2026-08-04T14:33:37.190Z</t>
   </si>
   <si>
     <t>TC-FUNC-024</t>
@@ -791,7 +791,7 @@
     <t>Verify Navigation Drawer Progress Report item click action</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:39.106Z</t>
+    <t>2026-08-04T14:33:37.224Z</t>
   </si>
   <si>
     <t>TC-FUNC-025</t>
@@ -800,7 +800,7 @@
     <t>Verify Navigation Drawer Help &amp; Support item click action</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:39.128Z</t>
+    <t>2026-08-04T14:33:37.257Z</t>
   </si>
   <si>
     <t>TC-FUNC-026</t>
@@ -809,7 +809,7 @@
     <t>Verify Navigation Drawer About App item click action</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:39.153Z</t>
+    <t>2026-08-04T14:33:37.287Z</t>
   </si>
   <si>
     <t>TC-FUNC-027</t>
@@ -818,7 +818,7 @@
     <t>Verify Navigation Drawer Tips Library item click action</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:39.176Z</t>
+    <t>2026-08-04T14:33:37.323Z</t>
   </si>
   <si>
     <t>TC-FUNC-028</t>
@@ -827,7 +827,7 @@
     <t>Verify Navigation Drawer Achievements item click action</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:39.198Z</t>
+    <t>2026-08-04T14:33:37.357Z</t>
   </si>
   <si>
     <t>TC-FUNC-029</t>
@@ -836,7 +836,7 @@
     <t>Verify Start Practice Session button click on Home Screen</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:39.224Z</t>
+    <t>2026-08-04T14:33:37.390Z</t>
   </si>
   <si>
     <t>TC-FUNC-030</t>
@@ -845,7 +845,7 @@
     <t>Verify Camera permission auto-grant via fake media flags</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:39.256Z</t>
+    <t>2026-08-04T14:33:37.423Z</t>
   </si>
   <si>
     <t>TC-FUNC-031</t>
@@ -854,7 +854,7 @@
     <t>Verify video preview stream rendering in HTML5 canvas element</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:39.291Z</t>
+    <t>2026-08-04T14:33:37.457Z</t>
   </si>
   <si>
     <t>TC-FUNC-032</t>
@@ -863,7 +863,7 @@
     <t>Verify Live posture tracking start recording toggle</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:39.314Z</t>
+    <t>2026-08-04T14:33:37.490Z</t>
   </si>
   <si>
     <t>TC-FUNC-033</t>
@@ -872,7 +872,7 @@
     <t>Verify Live recording duration timer count-up (MM:SS)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:39.342Z</t>
+    <t>2026-08-04T14:33:37.523Z</t>
   </si>
   <si>
     <t>TC-FUNC-034</t>
@@ -881,7 +881,7 @@
     <t>Verify Live posture real-time score overlay calculation</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:39.374Z</t>
+    <t>2026-08-04T14:33:37.557Z</t>
   </si>
   <si>
     <t>TC-FUNC-035</t>
@@ -890,7 +890,7 @@
     <t>Verify Live head stability angle tracking feed</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:39.407Z</t>
+    <t>2026-08-04T14:33:37.590Z</t>
   </si>
   <si>
     <t>TC-FUNC-036</t>
@@ -899,7 +899,7 @@
     <t>Verify Live gesture feedback indicators during recording</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:39.440Z</t>
+    <t>2026-08-04T14:33:37.623Z</t>
   </si>
   <si>
     <t>TC-FUNC-037</t>
@@ -908,7 +908,7 @@
     <t>Verify Stop Practice Session recording action</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:39.472Z</t>
+    <t>2026-08-04T14:33:37.657Z</t>
   </si>
   <si>
     <t>TC-FUNC-038</t>
@@ -917,7 +917,7 @@
     <t>Verify AI Analysis pipeline payload compilation and dispatch</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:39.547Z</t>
+    <t>2026-08-04T14:33:37.690Z</t>
   </si>
   <si>
     <t>TC-FUNC-039</t>
@@ -926,7 +926,7 @@
     <t>Verify Analysis Results Screen automatic navigation</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:39.581Z</t>
+    <t>2026-08-04T14:33:37.724Z</t>
   </si>
   <si>
     <t>TC-FUNC-040</t>
@@ -935,7 +935,7 @@
     <t>Verify Overall Confidence Score gauge display (0-100%)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:39.602Z</t>
+    <t>2026-08-04T14:33:37.757Z</t>
   </si>
   <si>
     <t>TC-FUNC-041</t>
@@ -944,7 +944,7 @@
     <t>Verify Posture Sub-Score card breakdown (40% weight)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:39.629Z</t>
+    <t>2026-08-04T14:33:37.790Z</t>
   </si>
   <si>
     <t>TC-FUNC-042</t>
@@ -953,7 +953,7 @@
     <t>Verify Head Stability Sub-Score card breakdown (30% weight)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:39.658Z</t>
+    <t>2026-08-04T14:33:37.824Z</t>
   </si>
   <si>
     <t>TC-FUNC-043</t>
@@ -962,7 +962,7 @@
     <t>Verify Gesture Activity Sub-Score card breakdown (30% weight)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:39.690Z</t>
+    <t>2026-08-04T14:33:37.854Z</t>
   </si>
   <si>
     <t>TC-FUNC-044</t>
@@ -971,7 +971,7 @@
     <t>Verify Key Recommendations list population based on posture AI</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:39.721Z</t>
+    <t>2026-08-04T14:33:37.879Z</t>
   </si>
   <si>
     <t>TC-FUNC-045</t>
@@ -980,7 +980,7 @@
     <t>Verify Save Practice Session to History SharedPreferences db</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:39.744Z</t>
+    <t>2026-08-04T14:33:37.907Z</t>
   </si>
   <si>
     <t>TC-FUNC-046</t>
@@ -989,7 +989,7 @@
     <t>Verify Export Session Report CSV button click action</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:39.775Z</t>
+    <t>2026-08-04T14:33:37.940Z</t>
   </si>
   <si>
     <t>TC-FUNC-047</t>
@@ -998,7 +998,7 @@
     <t>Verify Export Session Summary PDF document generator action</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:39.805Z</t>
+    <t>2026-08-04T14:33:37.972Z</t>
   </si>
   <si>
     <t>TC-FUNC-048</t>
@@ -1007,7 +1007,7 @@
     <t>Verify Session History log list updated with latest session</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:39.836Z</t>
+    <t>2026-08-04T14:33:38.006Z</t>
   </si>
   <si>
     <t>TC-FUNC-049</t>
@@ -1016,7 +1016,7 @@
     <t>Verify Session Comparison modal trigger for last 2 sessions</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:39.867Z</t>
+    <t>2026-08-04T14:33:38.031Z</t>
   </si>
   <si>
     <t>TC-FUNC-050</t>
@@ -1025,7 +1025,7 @@
     <t>Verify Clear History confirmation dialog action</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:39.891Z</t>
+    <t>2026-08-04T14:33:38.057Z</t>
   </si>
   <si>
     <t>TC-FUNC-051</t>
@@ -1034,7 +1034,7 @@
     <t>Verify Settings screen: Ocean Blue accent swatch selection</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:39.922Z</t>
+    <t>2026-08-04T14:33:38.088Z</t>
   </si>
   <si>
     <t>TC-FUNC-052</t>
@@ -1043,7 +1043,7 @@
     <t>Verify Settings screen: Sunset Orange accent swatch selection</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:39.953Z</t>
+    <t>2026-08-04T14:33:38.118Z</t>
   </si>
   <si>
     <t>TC-FUNC-053</t>
@@ -1052,7 +1052,7 @@
     <t>Verify Settings screen: Forest Green accent swatch selection</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:39.974Z</t>
+    <t>2026-08-04T14:33:38.153Z</t>
   </si>
   <si>
     <t>TC-FUNC-054</t>
@@ -1061,7 +1061,7 @@
     <t>Verify Dark Mode switch toggle ON</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:40.002Z</t>
+    <t>2026-08-04T14:33:38.184Z</t>
   </si>
   <si>
     <t>TC-FUNC-055</t>
@@ -1070,7 +1070,7 @@
     <t>Verify Dark Mode switch toggle OFF</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:40.032Z</t>
+    <t>2026-08-04T14:33:38.207Z</t>
   </si>
   <si>
     <t>TC-FUNC-056</t>
@@ -1079,7 +1079,7 @@
     <t>Verify Edit Profile screen form text field editable controllers</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:40.058Z</t>
+    <t>2026-08-04T14:33:38.240Z</t>
   </si>
   <si>
     <t>TC-FUNC-057</t>
@@ -1088,7 +1088,7 @@
     <t>Verify Edit Profile Save Changes button state commitment</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:40.086Z</t>
+    <t>2026-08-04T14:33:38.272Z</t>
   </si>
   <si>
     <t>TC-FUNC-058</t>
@@ -1097,7 +1097,7 @@
     <t>Verify Bottom Navigation Bar tab switching (Home, History, Profile, Settings)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:40.115Z</t>
+    <t>2026-08-04T14:33:38.307Z</t>
   </si>
   <si>
     <t>TC-FUNC-059</t>
@@ -1106,7 +1106,7 @@
     <t>Verify App Bar back button stack pop route resolution</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:40.137Z</t>
+    <t>2026-08-04T14:33:38.340Z</t>
   </si>
   <si>
     <t>TC-FUNC-060</t>
@@ -1115,7 +1115,7 @@
     <t>Verify Deep linking route resolution for /history and /settings URLs</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:40.162Z</t>
+    <t>2026-08-04T14:33:38.370Z</t>
   </si>
   <si>
     <t>TC-VAL-001</t>
@@ -1130,7 +1130,7 @@
     <t>Validate empty email input rejection message on login submission</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:40.179Z</t>
+    <t>2026-08-04T14:33:38.390Z</t>
   </si>
   <si>
     <t>TC-VAL-002</t>
@@ -1139,7 +1139,7 @@
     <t>Validate email missing @ symbol format error check</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:40.208Z</t>
+    <t>2026-08-04T14:33:38.405Z</t>
   </si>
   <si>
     <t>TC-VAL-003</t>
@@ -1148,7 +1148,7 @@
     <t>Validate email missing TLD domain extension format error check</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:40.225Z</t>
+    <t>2026-08-04T14:33:38.421Z</t>
   </si>
   <si>
     <t>TC-VAL-004</t>
@@ -1157,7 +1157,7 @@
     <t>Validate email with subdomains (user@mail.confidai.com) accepted</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:40.240Z</t>
+    <t>2026-08-04T14:33:38.441Z</t>
   </si>
   <si>
     <t>TC-VAL-005</t>
@@ -1166,7 +1166,7 @@
     <t>Validate email with plus tags (user+test@confidai.com) accepted</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:40.269Z</t>
+    <t>2026-08-04T14:33:38.474Z</t>
   </si>
   <si>
     <t>TC-VAL-006</t>
@@ -1175,7 +1175,7 @@
     <t>Validate email containing leading/trailing whitespace auto-trimming</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:40.285Z</t>
+    <t>2026-08-04T14:33:38.491Z</t>
   </si>
   <si>
     <t>TC-VAL-007</t>
@@ -1184,7 +1184,7 @@
     <t>Validate password shorter than 6 characters error message</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:40.301Z</t>
+    <t>2026-08-04T14:33:38.512Z</t>
   </si>
   <si>
     <t>TC-VAL-008</t>
@@ -1193,7 +1193,7 @@
     <t>Validate empty password field submission error response</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:40.331Z</t>
+    <t>2026-08-04T14:33:38.527Z</t>
   </si>
   <si>
     <t>TC-VAL-009</t>
@@ -1202,7 +1202,7 @@
     <t>Validate strong password policy enforcement (upper, lower, digit, special)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:40.350Z</t>
+    <t>2026-08-04T14:33:38.557Z</t>
   </si>
   <si>
     <t>TC-VAL-010</t>
@@ -1211,7 +1211,7 @@
     <t>Validate registration password and confirm password mismatch error</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:40.375Z</t>
+    <t>2026-08-04T14:33:38.573Z</t>
   </si>
   <si>
     <t>TC-VAL-011</t>
@@ -1220,7 +1220,7 @@
     <t>Validate registration full name empty input rejection</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:40.396Z</t>
+    <t>2026-08-04T14:33:38.600Z</t>
   </si>
   <si>
     <t>TC-VAL-012</t>
@@ -1229,7 +1229,7 @@
     <t>Validate registration full name max length boundary (100 chars)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:40.418Z</t>
+    <t>2026-08-04T14:33:38.618Z</t>
   </si>
   <si>
     <t>TC-VAL-013</t>
@@ -1238,7 +1238,7 @@
     <t>Validate registration phone number non-numeric character rejection</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:40.448Z</t>
+    <t>2026-08-04T14:33:38.640Z</t>
   </si>
   <si>
     <t>TC-VAL-014</t>
@@ -1247,7 +1247,7 @@
     <t>Validate phone number valid length boundary (10-15 digits)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:40.464Z</t>
+    <t>2026-08-04T14:33:38.674Z</t>
   </si>
   <si>
     <t>TC-VAL-015</t>
@@ -1256,7 +1256,7 @@
     <t>Validate OTP code submission with incomplete 5 digits</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:40.481Z</t>
+    <t>2026-08-04T14:33:38.690Z</t>
   </si>
   <si>
     <t>TC-VAL-016</t>
@@ -1265,7 +1265,7 @@
     <t>Validate OTP code submission with invalid alpha characters</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:40.508Z</t>
+    <t>2026-08-04T14:33:38.707Z</t>
   </si>
   <si>
     <t>TC-VAL-017</t>
@@ -1274,7 +1274,7 @@
     <t>Validate Terms of Service mandatory checkbox toggle check</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:40.525Z</t>
+    <t>2026-08-04T14:33:38.722Z</t>
   </si>
   <si>
     <t>TC-VAL-018</t>
@@ -1283,7 +1283,7 @@
     <t>Validate SQL injection attack string input in search field (` OR 1=1 --)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:40.540Z</t>
+    <t>2026-08-04T14:33:38.740Z</t>
   </si>
   <si>
     <t>TC-VAL-019</t>
@@ -1292,7 +1292,7 @@
     <t>Validate HTML script tag input in profile bio field (&lt;script&gt;alert(1)&lt;/script&gt;)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:40.567Z</t>
+    <t>2026-08-04T14:33:38.757Z</t>
   </si>
   <si>
     <t>TC-VAL-020</t>
@@ -1301,7 +1301,7 @@
     <t>Validate unicode special characters input in bio field (emoji, accents)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:40.586Z</t>
+    <t>2026-08-04T14:33:38.774Z</t>
   </si>
   <si>
     <t>TC-VAL-021</t>
@@ -1310,7 +1310,7 @@
     <t>Validate profile bio character count limit boundary (500 chars max)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:40.606Z</t>
+    <t>2026-08-04T14:33:38.789Z</t>
   </si>
   <si>
     <t>TC-VAL-022</t>
@@ -1319,7 +1319,7 @@
     <t>Validate practice session target score bounds (0 to 100%)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:40.629Z</t>
+    <t>2026-08-04T14:33:38.807Z</t>
   </si>
   <si>
     <t>TC-VAL-023</t>
@@ -1328,7 +1328,7 @@
     <t>Validate posture threshold angle bounds (0 to 90 degrees)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:40.650Z</t>
+    <t>2026-08-04T14:33:38.823Z</t>
   </si>
   <si>
     <t>TC-VAL-024</t>
@@ -1337,7 +1337,7 @@
     <t>Validate audio frequency input range bounds (20Hz - 20000Hz)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:40.672Z</t>
+    <t>2026-08-04T14:33:38.840Z</t>
   </si>
   <si>
     <t>TC-VAL-025</t>
@@ -1346,7 +1346,7 @@
     <t>Validate video frame rate FPS threshold drop handling (&lt;15 FPS alert)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:40.698Z</t>
+    <t>2026-08-04T14:33:38.857Z</t>
   </si>
   <si>
     <t>TC-VAL-026</t>
@@ -1355,7 +1355,7 @@
     <t>Validate session duration timer upper bound safety cap (120 mins)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:40.722Z</t>
+    <t>2026-08-04T14:33:38.881Z</t>
   </si>
   <si>
     <t>TC-VAL-027</t>
@@ -1364,7 +1364,7 @@
     <t>Validate session comparison calculation with missing session data</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:40.752Z</t>
+    <t>2026-08-04T14:33:38.907Z</t>
   </si>
   <si>
     <t>TC-VAL-028</t>
@@ -1373,7 +1373,7 @@
     <t>Validate clear history action when history log is empty</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:40.782Z</t>
+    <t>2026-08-04T14:33:38.923Z</t>
   </si>
   <si>
     <t>TC-VAL-029</t>
@@ -1382,7 +1382,7 @@
     <t>Validate export CSV trigger when no session records exist</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:40.798Z</t>
+    <t>2026-08-04T14:33:38.940Z</t>
   </si>
   <si>
     <t>TC-VAL-030</t>
@@ -1391,7 +1391,7 @@
     <t>Validate export PDF summary trigger when no session records exist</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:40.825Z</t>
+    <t>2026-08-04T14:33:38.958Z</t>
   </si>
   <si>
     <t>TC-VAL-031</t>
@@ -1400,7 +1400,7 @@
     <t>Validate setting theme color with invalid hex string code</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:40.841Z</t>
+    <t>2026-08-04T14:33:38.990Z</t>
   </si>
   <si>
     <t>TC-VAL-032</t>
@@ -1409,7 +1409,7 @@
     <t>Validate dark mode toggle rapid state clicking idempotency</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:40.858Z</t>
+    <t>2026-08-04T14:33:39.007Z</t>
   </si>
   <si>
     <t>TC-VAL-033</t>
@@ -1418,7 +1418,7 @@
     <t>Validate session token expiration timestamp validation guard</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:40.873Z</t>
+    <t>2026-08-04T14:33:39.023Z</t>
   </si>
   <si>
     <t>TC-VAL-034</t>
@@ -1427,7 +1427,7 @@
     <t>Validate local storage state corrupted JSON recovery fallback</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:40.891Z</t>
+    <t>2026-08-04T14:33:39.040Z</t>
   </si>
   <si>
     <t>TC-VAL-035</t>
@@ -1436,7 +1436,7 @@
     <t>Validate API error response status code 500 alert dialog</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:40.908Z</t>
+    <t>2026-08-04T14:33:39.057Z</t>
   </si>
   <si>
     <t>TC-VAL-036</t>
@@ -1445,7 +1445,7 @@
     <t>Validate API timeout (408) retry policy execution</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:40.925Z</t>
+    <t>2026-08-04T14:33:39.071Z</t>
   </si>
   <si>
     <t>TC-VAL-037</t>
@@ -1454,7 +1454,7 @@
     <t>Validate unauthorized API request (401) automatic redirect to Login</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:40.955Z</t>
+    <t>2026-08-04T14:33:39.140Z</t>
   </si>
   <si>
     <t>TC-VAL-038</t>
@@ -1463,7 +1463,7 @@
     <t>Validate forbidden access route (403) access denied banner</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:40.973Z</t>
+    <t>2026-08-04T14:33:39.174Z</t>
   </si>
   <si>
     <t>TC-VAL-039</t>
@@ -1472,7 +1472,7 @@
     <t>Validate URL route parameter type validation (/history?id=abc vs int)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:40.989Z</t>
+    <t>2026-08-04T14:33:39.195Z</t>
   </si>
   <si>
     <t>TC-VAL-040</t>
@@ -1481,7 +1481,7 @@
     <t>Validate query string param sanitization against path traversal</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:41.008Z</t>
+    <t>2026-08-04T14:33:39.215Z</t>
   </si>
   <si>
     <t>TC-VAL-041</t>
@@ -1490,7 +1490,7 @@
     <t>Validate camera device missing hardware exception handling</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:41.025Z</t>
+    <t>2026-08-04T14:33:39.247Z</t>
   </si>
   <si>
     <t>TC-VAL-042</t>
@@ -1499,7 +1499,7 @@
     <t>Validate microphone permission denied audio stream fallback</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:41.062Z</t>
+    <t>2026-08-04T14:33:39.272Z</t>
   </si>
   <si>
     <t>TC-VAL-043</t>
@@ -1508,7 +1508,7 @@
     <t>Validate low bandwidth network degradation video stream downscaling</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:41.091Z</t>
+    <t>2026-08-04T14:33:39.287Z</t>
   </si>
   <si>
     <t>TC-VAL-044</t>
@@ -1517,7 +1517,7 @@
     <t>Validate invalid image file upload format for avatar (.txt rejected)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:41.107Z</t>
+    <t>2026-08-04T14:33:39.303Z</t>
   </si>
   <si>
     <t>TC-VAL-045</t>
@@ -1526,7 +1526,7 @@
     <t>Validate avatar image file size upper limit boundary (&gt;5MB rejected)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:41.124Z</t>
+    <t>2026-08-04T14:33:39.326Z</t>
   </si>
   <si>
     <t>TC-VAL-046</t>
@@ -1535,7 +1535,7 @@
     <t>Validate streak start date calculation across leap years</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:41.158Z</t>
+    <t>2026-08-04T14:33:39.355Z</t>
   </si>
   <si>
     <t>TC-VAL-047</t>
@@ -1544,7 +1544,7 @@
     <t>Validate timezone offset shifts during daily streak calculation</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:41.174Z</t>
+    <t>2026-08-04T14:33:39.371Z</t>
   </si>
   <si>
     <t>TC-VAL-048</t>
@@ -1553,7 +1553,7 @@
     <t>Validate form submission double-click duplicate request prevention</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:41.191Z</t>
+    <t>2026-08-04T14:33:39.391Z</t>
   </si>
   <si>
     <t>TC-VAL-049</t>
@@ -1562,7 +1562,7 @@
     <t>Validate password visibility toggle state persistence during typing</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:41.207Z</t>
+    <t>2026-08-04T14:33:39.414Z</t>
   </si>
   <si>
     <t>TC-VAL-050</t>
@@ -1571,7 +1571,7 @@
     <t>Validate default form input reset button clearing all fields</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:41.224Z</t>
+    <t>2026-08-04T14:33:39.441Z</t>
   </si>
   <si>
     <t>TC-UI-001</t>
@@ -1586,7 +1586,7 @@
     <t>Verify responsive layout adaptation at 1920x1080 Full HD Desktop resolution</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:41.241Z</t>
+    <t>2026-08-04T14:33:39.472Z</t>
   </si>
   <si>
     <t>TC-UI-002</t>
@@ -1595,7 +1595,7 @@
     <t>Verify responsive layout adaptation at 1440x900 WXGA Laptop resolution</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:41.257Z</t>
+    <t>2026-08-04T14:33:39.488Z</t>
   </si>
   <si>
     <t>TC-UI-003</t>
@@ -1604,7 +1604,7 @@
     <t>Verify responsive layout adaptation at 1280x800 Standard Desktop resolution</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:41.274Z</t>
+    <t>2026-08-04T14:33:39.513Z</t>
   </si>
   <si>
     <t>TC-UI-004</t>
@@ -1613,7 +1613,7 @@
     <t>Verify responsive layout adaptation at 768x1024 Tablet Portrait viewport</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:41.291Z</t>
+    <t>2026-08-04T14:33:39.537Z</t>
   </si>
   <si>
     <t>TC-UI-005</t>
@@ -1622,7 +1622,7 @@
     <t>Verify responsive layout adaptation at 375x812 Mobile Web viewport</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:41.309Z</t>
+    <t>2026-08-04T14:33:39.553Z</t>
   </si>
   <si>
     <t>TC-UI-006</t>
@@ -1631,7 +1631,7 @@
     <t>Verify responsive layout adaptation at 320x568 Small Mobile viewport</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:41.324Z</t>
+    <t>2026-08-04T14:33:39.569Z</t>
   </si>
   <si>
     <t>TC-UI-007</t>
@@ -1640,7 +1640,7 @@
     <t>Verify Flutter web semantics tree accessibility node tree rendering</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:41.341Z</t>
+    <t>2026-08-04T14:33:39.589Z</t>
   </si>
   <si>
     <t>TC-UI-008</t>
@@ -1649,7 +1649,7 @@
     <t>Verify ARIA accessibility labels for screen reader compatibility on controls</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:41.358Z</t>
+    <t>2026-08-04T14:33:39.604Z</t>
   </si>
   <si>
     <t>TC-UI-009</t>
@@ -1658,7 +1658,7 @@
     <t>Verify color contrast ratio WCAG AAA standards for all text elements</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:41.375Z</t>
+    <t>2026-08-04T14:33:39.621Z</t>
   </si>
   <si>
     <t>TC-UI-010</t>
@@ -1667,7 +1667,7 @@
     <t>Verify font loading and Google Inter/Outfit typography hierarchy scaling</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:41.390Z</t>
+    <t>2026-08-04T14:33:39.641Z</t>
   </si>
   <si>
     <t>TC-UI-011</t>
@@ -1676,7 +1676,7 @@
     <t>Verify glassmorphism card backdrop filter blur effect rendering</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:41.408Z</t>
+    <t>2026-08-04T14:33:39.657Z</t>
   </si>
   <si>
     <t>TC-UI-012</t>
@@ -1685,7 +1685,7 @@
     <t>Verify card elevation box-shadow smooth multi-layered rendering</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:41.424Z</t>
+    <t>2026-08-04T14:33:39.672Z</t>
   </si>
   <si>
     <t>TC-UI-013</t>
@@ -1694,7 +1694,7 @@
     <t>Verify dynamic gradient background rendering in Light Theme mode</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:41.441Z</t>
+    <t>2026-08-04T14:33:39.688Z</t>
   </si>
   <si>
     <t>TC-UI-014</t>
@@ -1703,7 +1703,7 @@
     <t>Verify dark mode sleek palette transition (#121212 background)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:41.458Z</t>
+    <t>2026-08-04T14:33:39.711Z</t>
   </si>
   <si>
     <t>TC-UI-015</t>
@@ -1712,7 +1712,7 @@
     <t>Verify micro-animation smooth transition on hoverable action buttons</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:41.474Z</t>
+    <t>2026-08-04T14:33:39.741Z</t>
   </si>
   <si>
     <t>TC-UI-016</t>
@@ -1721,7 +1721,7 @@
     <t>Verify modal bottom sheet backdrop blur overlay rendering</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:41.491Z</t>
+    <t>2026-08-04T14:33:39.770Z</t>
   </si>
   <si>
     <t>TC-UI-017</t>
@@ -1730,7 +1730,7 @@
     <t>Verify Material Icons vector rendering consistency across all screens</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:41.508Z</t>
+    <t>2026-08-04T14:33:39.786Z</t>
   </si>
   <si>
     <t>TC-UI-018</t>
@@ -1739,7 +1739,7 @@
     <t>Verify keyboard navigation tab focus ring outline visibility</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:41.524Z</t>
+    <t>2026-08-04T14:33:39.802Z</t>
   </si>
   <si>
     <t>TC-UI-019</t>
@@ -1748,7 +1748,7 @@
     <t>Verify screen reader announcements on live state changes</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:41.541Z</t>
+    <t>2026-08-04T14:33:39.826Z</t>
   </si>
   <si>
     <t>TC-UI-020</t>
@@ -1757,7 +1757,7 @@
     <t>Verify custom scrollbar styling and smooth scrolling physics</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:41.558Z</t>
+    <t>2026-08-04T14:33:39.857Z</t>
   </si>
   <si>
     <t>TC-UI-021</t>
@@ -1766,7 +1766,7 @@
     <t>Verify high-contrast accessibility mode theme toggle support</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:41.575Z</t>
+    <t>2026-08-04T14:33:39.887Z</t>
   </si>
   <si>
     <t>TC-UI-022</t>
@@ -1775,7 +1775,7 @@
     <t>Verify loading skeleton shimmer placeholder animation during asset fetch</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:41.591Z</t>
+    <t>2026-08-04T14:33:39.903Z</t>
   </si>
   <si>
     <t>TC-UI-023</t>
@@ -1784,7 +1784,7 @@
     <t>Verify tooltip popover hover display on dashboard metric cards</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:41.622Z</t>
+    <t>2026-08-04T14:33:39.919Z</t>
   </si>
   <si>
     <t>TC-UI-024</t>
@@ -1793,7 +1793,7 @@
     <t>Verify smooth page transition route slide &amp; fade animations</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:41.642Z</t>
+    <t>2026-08-04T14:33:39.935Z</t>
   </si>
   <si>
     <t>TC-UI-025</t>
@@ -1802,7 +1802,7 @@
     <t>Verify interactive posture score circular gauge progress animation</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:41.658Z</t>
+    <t>2026-08-04T14:33:39.956Z</t>
   </si>
   <si>
     <t>TC-UI-026</t>
@@ -1811,7 +1811,7 @@
     <t>Verify notification banner toast slide-in entry animation</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:41.689Z</t>
+    <t>2026-08-04T14:33:39.978Z</t>
   </si>
   <si>
     <t>TC-UI-027</t>
@@ -1820,7 +1820,7 @@
     <t>Verify badge icon glow effect on unlocking achievements</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:41.704Z</t>
+    <t>2026-08-04T14:33:39.997Z</t>
   </si>
   <si>
     <t>TC-UI-028</t>
@@ -1829,7 +1829,7 @@
     <t>Verify audio waveform canvas visualizer dynamic frequency bars</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:41.728Z</t>
+    <t>2026-08-04T14:33:40.021Z</t>
   </si>
   <si>
     <t>TC-UI-029</t>
@@ -1838,7 +1838,7 @@
     <t>Verify streak calendar day node active/inactive state styling</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:41.745Z</t>
+    <t>2026-08-04T14:33:40.037Z</t>
   </si>
   <si>
     <t>TC-UI-030</t>
@@ -1847,7 +1847,7 @@
     <t>Verify score pill badge background color mapping (Green/Yellow/Red)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:41.773Z</t>
+    <t>2026-08-04T14:33:40.060Z</t>
   </si>
   <si>
     <t>TC-UI-031</t>
@@ -1856,7 +1856,7 @@
     <t>Verify form input floating label transition animation on focus</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:41.788Z</t>
+    <t>2026-08-04T14:33:40.076Z</t>
   </si>
   <si>
     <t>TC-UI-032</t>
@@ -1865,7 +1865,7 @@
     <t>Verify error snackbar alert styling and auto-dismiss timer</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:41.806Z</t>
+    <t>2026-08-04T14:33:40.105Z</t>
   </si>
   <si>
     <t>TC-UI-033</t>
@@ -1874,7 +1874,7 @@
     <t>Verify app drawer user profile avatar circular clipping border</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:41.824Z</t>
+    <t>2026-08-04T14:33:40.121Z</t>
   </si>
   <si>
     <t>TC-UI-034</t>
@@ -1883,7 +1883,7 @@
     <t>Verify bottom navigation bar active tab icon highlight indicator</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:41.841Z</t>
+    <t>2026-08-04T14:33:40.138Z</t>
   </si>
   <si>
     <t>TC-UI-035</t>
@@ -1892,7 +1892,7 @@
     <t>Verify settings color swatch selected state checkmark icon overlay</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:41.858Z</t>
+    <t>2026-08-04T14:33:40.163Z</t>
   </si>
   <si>
     <t>TC-UI-036</t>
@@ -1901,7 +1901,7 @@
     <t>Verify session history card hover elevation shadow increase</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:41.876Z</t>
+    <t>2026-08-04T14:33:40.261Z</t>
   </si>
   <si>
     <t>TC-UI-037</t>
@@ -1910,7 +1910,7 @@
     <t>Verify accordion expandable list smooth height transition</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:41.891Z</t>
+    <t>2026-08-04T14:33:40.278Z</t>
   </si>
   <si>
     <t>TC-UI-038</t>
@@ -1919,7 +1919,7 @@
     <t>Verify chart tooltip crosshair hover tracking indicator</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:41.908Z</t>
+    <t>2026-08-04T14:33:40.575Z</t>
   </si>
   <si>
     <t>TC-UI-039</t>
@@ -1928,7 +1928,7 @@
     <t>Verify posture video preview aspect ratio framing container</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:41.925Z</t>
+    <t>2026-08-04T14:33:40.598Z</t>
   </si>
   <si>
     <t>TC-UI-040</t>
@@ -1937,7 +1937,7 @@
     <t>Verify floating action button (FAB) press scale down effect</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:41.941Z</t>
+    <t>2026-08-04T14:33:40.622Z</t>
   </si>
   <si>
     <t>TC-UI-041</t>
@@ -1946,7 +1946,7 @@
     <t>Verify dynamic text truncation with ellipsis for long session titles</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:41.958Z</t>
+    <t>2026-08-04T14:33:40.641Z</t>
   </si>
   <si>
     <t>TC-UI-042</t>
@@ -1955,7 +1955,7 @@
     <t>Verify empty state illustration and title text when no history exists</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:41.974Z</t>
+    <t>2026-08-04T14:33:40.656Z</t>
   </si>
   <si>
     <t>TC-UI-043</t>
@@ -1964,7 +1964,7 @@
     <t>Verify onboarding carousel pagination dot active indicator scaling</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:41.991Z</t>
+    <t>2026-08-04T14:33:40.673Z</t>
   </si>
   <si>
     <t>TC-UI-044</t>
@@ -1973,7 +1973,7 @@
     <t>Verify dark mode toggle switch thumb icon transition (Sun to Moon)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:42.008Z</t>
+    <t>2026-08-04T14:33:40.688Z</t>
   </si>
   <si>
     <t>TC-UI-045</t>
@@ -1982,7 +1982,7 @@
     <t>Verify dialog modal scale-in entrance transition animation</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:42.025Z</t>
+    <t>2026-08-04T14:33:40.703Z</t>
   </si>
   <si>
     <t>TC-UI-046</t>
@@ -1991,7 +1991,7 @@
     <t>Verify button ripple ripple effect animation on click trigger</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:42.042Z</t>
+    <t>2026-08-04T14:33:40.718Z</t>
   </si>
   <si>
     <t>TC-UI-047</t>
@@ -2000,7 +2000,7 @@
     <t>Verify minimum touch target dimensions (48x48px WCAG compliance)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:42.075Z</t>
+    <t>2026-08-04T14:33:40.740Z</t>
   </si>
   <si>
     <t>TC-UI-048</t>
@@ -2009,7 +2009,7 @@
     <t>Verify page scroll progress bar indicator fixed header positioning</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:42.091Z</t>
+    <t>2026-08-04T14:33:40.756Z</t>
   </si>
   <si>
     <t>TC-UI-049</t>
@@ -2018,7 +2018,7 @@
     <t>Verify dropdown menu items border radius and backdrop shadow styling</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:42.108Z</t>
+    <t>2026-08-04T14:33:40.771Z</t>
   </si>
   <si>
     <t>TC-UI-050</t>
@@ -2027,7 +2027,7 @@
     <t>Verify app footer copyright label and version tag typography rendering</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:42.123Z</t>
+    <t>2026-08-04T14:33:40.787Z</t>
   </si>
   <si>
     <t>TC-SEC-001</t>
@@ -2042,7 +2042,7 @@
     <t>Verify Cross-Site Scripting (XSS) payload sanitization in dynamic HTML content injection</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:42.141Z</t>
+    <t>2026-08-04T14:33:40.807Z</t>
   </si>
   <si>
     <t>TC-SEC-002</t>
@@ -2051,7 +2051,7 @@
     <t>Verify Cross-Site Request Forgery (CSRF) header validation on state-changing API requests</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:42.158Z</t>
+    <t>2026-08-04T14:33:40.824Z</t>
   </si>
   <si>
     <t>TC-SEC-003</t>
@@ -2060,7 +2060,7 @@
     <t>Verify Content-Security-Policy (CSP) headers present on web app response</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:42.175Z</t>
+    <t>2026-08-04T14:33:40.840Z</t>
   </si>
   <si>
     <t>TC-SEC-004</t>
@@ -2069,7 +2069,7 @@
     <t>Verify HTTP Strict Transport Security (HSTS) max-age directive compliance</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:42.191Z</t>
+    <t>2026-08-04T14:33:40.871Z</t>
   </si>
   <si>
     <t>TC-SEC-005</t>
@@ -2078,7 +2078,7 @@
     <t>Verify local session token encryption key standard (AES-256 local storage)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:42.208Z</t>
+    <t>2026-08-04T14:33:40.902Z</t>
   </si>
   <si>
     <t>TC-SEC-006</t>
@@ -2087,7 +2087,7 @@
     <t>Verify authentication session token automatic expiration after idle timeout</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:42.223Z</t>
+    <t>2026-08-04T14:33:40.919Z</t>
   </si>
   <si>
     <t>TC-SEC-007</t>
@@ -2096,7 +2096,7 @@
     <t>Verify Frame-Busting X-Frame-Options header (DENY / SAMEORIGIN) against clickjacking</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:42.241Z</t>
+    <t>2026-08-04T14:33:40.939Z</t>
   </si>
   <si>
     <t>TC-SEC-008</t>
@@ -2105,7 +2105,7 @@
     <t>Verify masking sensitive password characters in DOM element inspection</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:42.259Z</t>
+    <t>2026-08-04T14:33:40.954Z</t>
   </si>
   <si>
     <t>TC-SEC-009</t>
@@ -2114,7 +2114,7 @@
     <t>Verify Cross-Origin Resource Sharing (CORS) origin restriction headers</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:42.274Z</t>
+    <t>2026-08-04T14:33:40.971Z</t>
   </si>
   <si>
     <t>TC-SEC-010</t>
@@ -2123,7 +2123,7 @@
     <t>Verify rate limiting 429 Too Many Requests response handling on auth endpoints</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:42.291Z</t>
+    <t>2026-08-04T14:33:40.988Z</t>
   </si>
   <si>
     <t>TC-SEC-011</t>
@@ -2132,7 +2132,7 @@
     <t>Verify SQL injection payload sanitization on search filter text fields</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:42.308Z</t>
+    <t>2026-08-04T14:33:41.004Z</t>
   </si>
   <si>
     <t>TC-SEC-012</t>
@@ -2141,7 +2141,7 @@
     <t>Verify Secure Cookie flags (SameSite=Strict, Secure, HttpOnly) enforcement</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:42.324Z</t>
+    <t>2026-08-04T14:33:41.019Z</t>
   </si>
   <si>
     <t>TC-SEC-013</t>
@@ -2150,7 +2150,7 @@
     <t>Verify Open Redirect vulnerability protection on post-login callback parameters</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:42.358Z</t>
+    <t>2026-08-04T14:33:41.036Z</t>
   </si>
   <si>
     <t>TC-SEC-014</t>
@@ -2159,7 +2159,7 @@
     <t>Verify autocomplete=off attribute on sensitive auth password form fields</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:42.375Z</t>
+    <t>2026-08-04T14:33:41.057Z</t>
   </si>
   <si>
     <t>TC-SEC-015</t>
@@ -2168,7 +2168,7 @@
     <t>Verify Subresource Integrity (SRI) hash verification for external CDN scripts</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:42.391Z</t>
+    <t>2026-08-04T14:33:41.074Z</t>
   </si>
   <si>
     <t>TC-SEC-016</t>
@@ -2177,7 +2177,7 @@
     <t>Verify session fixation vulnerability protection (token regenerated on login)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:42.408Z</t>
+    <t>2026-08-04T14:33:41.090Z</t>
   </si>
   <si>
     <t>TC-SEC-017</t>
@@ -2186,7 +2186,7 @@
     <t>Verify TLS 1.3 protocol handshake encryption verification on HTTPS requests</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:42.424Z</t>
+    <t>2026-08-04T14:33:41.123Z</t>
   </si>
   <si>
     <t>TC-SEC-018</t>
@@ -2195,7 +2195,7 @@
     <t>Verify X-Content-Type-Options: nosniff header against MIME-type sniffing</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:42.440Z</t>
+    <t>2026-08-04T14:33:41.156Z</t>
   </si>
   <si>
     <t>TC-SEC-019</t>
@@ -2204,7 +2204,7 @@
     <t>Verify sensitive data purge from browser local storage on tab close / logout</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:42.458Z</t>
+    <t>2026-08-04T14:33:41.174Z</t>
   </si>
   <si>
     <t>TC-SEC-020</t>
@@ -2213,7 +2213,7 @@
     <t>Verify client-side Javascript bundle API key exposure audit scan</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:42.475Z</t>
+    <t>2026-08-04T14:33:41.198Z</t>
   </si>
   <si>
     <t>TC-SEC-021</t>
@@ -2222,7 +2222,7 @@
     <t>Verify password reset token single-use invalidation check</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:42.491Z</t>
+    <t>2026-08-04T14:33:41.222Z</t>
   </si>
   <si>
     <t>TC-SEC-022</t>
@@ -2231,7 +2231,7 @@
     <t>Verify DOM XSS protection when rendering dynamic user notes</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:42.508Z</t>
+    <t>2026-08-04T14:33:41.237Z</t>
   </si>
   <si>
     <t>TC-SEC-023</t>
@@ -2240,7 +2240,7 @@
     <t>Verify Referrer-Policy header (strict-origin-when-cross-origin) check</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:42.524Z</t>
+    <t>2026-08-04T14:33:41.253Z</t>
   </si>
   <si>
     <t>TC-SEC-024</t>
@@ -2249,7 +2249,7 @@
     <t>Verify Permissions-Policy header restricting camera/mic to app origin</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:42.540Z</t>
+    <t>2026-08-04T14:33:41.273Z</t>
   </si>
   <si>
     <t>TC-SEC-025</t>
@@ -2258,7 +2258,7 @@
     <t>Verify input sanitization on camera session export title field</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:42.558Z</t>
+    <t>2026-08-04T14:33:41.291Z</t>
   </si>
   <si>
     <t>TC-SEC-026</t>
@@ -2267,7 +2267,7 @@
     <t>Verify secure Web Socket (wss://) protocol enforcement for live pose stream</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:42.575Z</t>
+    <t>2026-08-04T14:33:41.317Z</t>
   </si>
   <si>
     <t>TC-SEC-027</t>
@@ -2276,7 +2276,7 @@
     <t>Verify sensitive user profile data masking in network request logs</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:42.591Z</t>
+    <t>2026-08-04T14:33:41.336Z</t>
   </si>
   <si>
     <t>TC-SEC-028</t>
@@ -2285,7 +2285,7 @@
     <t>Verify brute force password attempt account lockout policy</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:42.607Z</t>
+    <t>2026-08-04T14:33:41.352Z</t>
   </si>
   <si>
     <t>TC-SEC-029</t>
@@ -2294,7 +2294,7 @@
     <t>Verify authentication header Bearer token format compliance</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:42.623Z</t>
+    <t>2026-08-04T14:33:41.373Z</t>
   </si>
   <si>
     <t>TC-SEC-030</t>
@@ -2303,7 +2303,7 @@
     <t>Verify session storage tamper detection hash checksum verification</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:42.639Z</t>
+    <t>2026-08-04T14:33:41.396Z</t>
   </si>
   <si>
     <t>TC-SEC-031</t>
@@ -2312,7 +2312,7 @@
     <t>Verify HTTP GET request query string sensitivity audit (no passwords in URL)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:42.654Z</t>
+    <t>2026-08-04T14:33:41.422Z</t>
   </si>
   <si>
     <t>TC-SEC-032</t>
@@ -2321,7 +2321,7 @@
     <t>Verify HTML5 web storage quota exhaustion vulnerability protection</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:42.678Z</t>
+    <t>2026-08-04T14:33:41.438Z</t>
   </si>
   <si>
     <t>TC-SEC-033</t>
@@ -2330,7 +2330,7 @@
     <t>Verify anti-automation bot detection reCAPTCHA challenge readiness</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:42.707Z</t>
+    <t>2026-08-04T14:33:41.462Z</t>
   </si>
   <si>
     <t>TC-SEC-034</t>
@@ -2339,7 +2339,7 @@
     <t>Verify dynamic JS eval() function execution ban in web client runtime</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:42.723Z</t>
+    <t>2026-08-04T14:33:41.492Z</t>
   </si>
   <si>
     <t>TC-SEC-035</t>
@@ -2348,7 +2348,7 @@
     <t>Verify cross-domain window postMessage targetOrigin validation</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:42.738Z</t>
+    <t>2026-08-04T14:33:41.515Z</t>
   </si>
   <si>
     <t>TC-SEC-036</t>
@@ -2357,7 +2357,7 @@
     <t>Verify third-party dependency vulnerability scanning check (npm audit)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:42.753Z</t>
+    <t>2026-08-04T14:33:41.530Z</t>
   </si>
   <si>
     <t>TC-SEC-037</t>
@@ -2366,7 +2366,7 @@
     <t>Verify user profile password update mandatory current password check</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:42.776Z</t>
+    <t>2026-08-04T14:33:41.546Z</t>
   </si>
   <si>
     <t>TC-SEC-038</t>
@@ -2375,7 +2375,7 @@
     <t>Verify Session token revoked immediately on password change</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:42.805Z</t>
+    <t>2026-08-04T14:33:41.564Z</t>
   </si>
   <si>
     <t>TC-SEC-039</t>
@@ -2384,7 +2384,7 @@
     <t>Verify secure HTTPS redirect from unencrypted http:// requests</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:42.822Z</t>
+    <t>2026-08-04T14:33:41.588Z</t>
   </si>
   <si>
     <t>TC-SEC-040</t>
@@ -2393,7 +2393,7 @@
     <t>Verify security contact security.txt file availability on domain root</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:42.841Z</t>
+    <t>2026-08-04T14:33:41.603Z</t>
   </si>
   <si>
     <t>TC-PERF-001</t>
@@ -2408,7 +2408,7 @@
     <t>Verify First Contentful Paint (FCP) load time metric (&lt;1.2 seconds target)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:42.866Z</t>
+    <t>2026-08-04T14:33:41.628Z</t>
   </si>
   <si>
     <t>TC-PERF-002</t>
@@ -2417,7 +2417,7 @@
     <t>Verify Time to Interactive (TTI) web application load metric (&lt;1.5 seconds)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:42.882Z</t>
+    <t>2026-08-04T14:33:41.646Z</t>
   </si>
   <si>
     <t>TC-PERF-003</t>
@@ -2426,7 +2426,7 @@
     <t>Verify Largest Contentful Paint (LCP) render latency (&lt;1.8 seconds)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:42.912Z</t>
+    <t>2026-08-04T14:33:41.668Z</t>
   </si>
   <si>
     <t>TC-PERF-004</t>
@@ -2435,7 +2435,7 @@
     <t>Verify Cumulative Layout Shift (CLS) layout stability score (&lt;0.05 index)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:42.941Z</t>
+    <t>2026-08-04T14:33:41.690Z</t>
   </si>
   <si>
     <t>TC-PERF-005</t>
@@ -2444,7 +2444,7 @@
     <t>Verify First Input Delay (FID) interactivity response latency (&lt;25ms)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:42.956Z</t>
+    <t>2026-08-04T14:33:41.717Z</t>
   </si>
   <si>
     <t>TC-PERF-006</t>
@@ -2453,7 +2453,7 @@
     <t>Verify DOM Tree node count upper bound limit (&lt;1500 total elements)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:42.972Z</t>
+    <t>2026-08-04T14:33:41.737Z</t>
   </si>
   <si>
     <t>TC-PERF-007</t>
@@ -2462,7 +2462,7 @@
     <t>Verify camera posture tracking stream frame rate stability (60 FPS target)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:42.991Z</t>
+    <t>2026-08-04T14:33:41.753Z</t>
   </si>
   <si>
     <t>TC-PERF-008</t>
@@ -2471,7 +2471,7 @@
     <t>Verify Async Web Worker pose inference processing latency (&lt;12ms per frame)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:43.007Z</t>
+    <t>2026-08-04T14:33:41.769Z</t>
   </si>
   <si>
     <t>TC-PERF-009</t>
@@ -2480,7 +2480,7 @@
     <t>Verify MediaStream canvas buffer memory garbage collection (&lt;5MB allocation)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:43.022Z</t>
+    <t>2026-08-04T14:33:41.785Z</t>
   </si>
   <si>
     <t>TC-PERF-010</t>
@@ -2489,7 +2489,7 @@
     <t>Verify WebGL canvas hardware acceleration shader compilation time (&lt;50ms)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:43.048Z</t>
+    <t>2026-08-04T14:33:41.804Z</t>
   </si>
   <si>
     <t>TC-PERF-011</t>
@@ -2498,7 +2498,7 @@
     <t>Verify web main bundle JS gzip payload file size (&lt;2.8MB total bundle)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:43.073Z</t>
+    <t>2026-08-04T14:33:41.825Z</t>
   </si>
   <si>
     <t>TC-PERF-012</t>
@@ -2507,7 +2507,7 @@
     <t>Verify HTTP/2 multiplexed asset request pipeline parallel loading throughput</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:43.090Z</t>
+    <t>2026-08-04T14:33:41.840Z</t>
   </si>
   <si>
     <t>TC-PERF-013</t>
@@ -2516,7 +2516,7 @@
     <t>Verify browser HTTP cache hit ratio for static web build assets (&gt;95% ratio)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:43.107Z</t>
+    <t>2026-08-04T14:33:41.856Z</t>
   </si>
   <si>
     <t>TC-PERF-014</t>
@@ -2525,7 +2525,7 @@
     <t>Verify high concurrency simulated pose data stream event throughput (100 ev/sec)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:43.124Z</t>
+    <t>2026-08-04T14:33:41.871Z</t>
   </si>
   <si>
     <t>TC-PERF-015</t>
@@ -2534,7 +2534,7 @@
     <t>Verify memory leak check under 10-minute continuous camera session simulation</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:43.143Z</t>
+    <t>2026-08-04T14:33:41.887Z</t>
   </si>
   <si>
     <t>TC-PERF-016</t>
@@ -2543,7 +2543,7 @@
     <t>Verify network response latency under simulated 3G network throttling</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:43.158Z</t>
+    <t>2026-08-04T14:33:41.903Z</t>
   </si>
   <si>
     <t>TC-PERF-017</t>
@@ -2552,7 +2552,7 @@
     <t>Verify dynamic asset lazy loading image response performance</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:43.176Z</t>
+    <t>2026-08-04T14:33:41.918Z</t>
   </si>
   <si>
     <t>TC-PERF-018</t>
@@ -2561,7 +2561,7 @@
     <t>Verify list virtualization smooth scrolling FPS efficiency (60 FPS list view)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:43.205Z</t>
+    <t>2026-08-04T14:33:41.934Z</t>
   </si>
   <si>
     <t>TC-PERF-019</t>
@@ -2570,7 +2570,7 @@
     <t>Verify Web Socket event loop latency during live metrics streaming (&lt;15ms)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:43.221Z</t>
+    <t>2026-08-04T14:33:41.950Z</t>
   </si>
   <si>
     <t>TC-PERF-020</t>
@@ -2579,7 +2579,7 @@
     <t>Verify LocalStorage key-value read/write throughput stress test (1000 ops/sec)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:43.236Z</t>
+    <t>2026-08-04T14:33:41.974Z</t>
   </si>
   <si>
     <t>TC-PERF-021</t>
@@ -2588,7 +2588,7 @@
     <t>Verify CPU utilization stability during continuous AI posture processing (&lt;25%)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:43.253Z</t>
+    <t>2026-08-04T14:33:41.989Z</t>
   </si>
   <si>
     <t>TC-PERF-022</t>
@@ -2597,7 +2597,7 @@
     <t>Verify rapid consecutive route navigation switching stress test (20 route changes)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:43.274Z</t>
+    <t>2026-08-04T14:33:42.006Z</t>
   </si>
   <si>
     <t>TC-PERF-023</t>
@@ -2606,7 +2606,7 @@
     <t>Verify audio pitch autocorrelation processing time per 100ms sample block (&lt;5ms)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:43.305Z</t>
+    <t>2026-08-04T14:33:42.021Z</t>
   </si>
   <si>
     <t>TC-PERF-024</t>
@@ -2615,7 +2615,7 @@
     <t>Verify PDF report compilation duration for 100 session records (&lt;800ms)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:43.320Z</t>
+    <t>2026-08-04T14:33:42.037Z</t>
   </si>
   <si>
     <t>TC-PERF-025</t>
@@ -2624,7 +2624,7 @@
     <t>Verify CSV report generation and blob URL creation duration (&lt;100ms)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:43.336Z</t>
+    <t>2026-08-04T14:33:42.061Z</t>
   </si>
   <si>
     <t>TC-PERF-026</t>
@@ -2633,7 +2633,7 @@
     <t>Verify initial Flutter engine WebAssembly WASM module load time (&lt;600ms)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:43.358Z</t>
+    <t>2026-08-04T14:33:42.076Z</t>
   </si>
   <si>
     <t>TC-PERF-027</t>
@@ -2642,7 +2642,7 @@
     <t>Verify font rendering swap display strategy (font-display: swap compliance)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:43.374Z</t>
+    <t>2026-08-04T14:33:42.092Z</t>
   </si>
   <si>
     <t>TC-PERF-028</t>
@@ -2651,7 +2651,7 @@
     <t>Verify CSS backdrop-filter render latency on low-spec GPU devices (&lt;10ms)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:43.391Z</t>
+    <t>2026-08-04T14:33:42.108Z</t>
   </si>
   <si>
     <t>TC-PERF-029</t>
@@ -2660,7 +2660,7 @@
     <t>Verify SharedPreferences sync commit latency on bulk 50 session write</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:43.406Z</t>
+    <t>2026-08-04T14:33:42.124Z</t>
   </si>
   <si>
     <t>TC-PERF-030</t>
@@ -2669,7 +2669,7 @@
     <t>Verify image asset preloading cache initialization latency</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:43.422Z</t>
+    <t>2026-08-04T14:33:42.140Z</t>
   </si>
   <si>
     <t>TC-PERF-031</t>
@@ -2678,7 +2678,7 @@
     <t>Verify DOM reflow and repaint count reduction during animation</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:43.447Z</t>
+    <t>2026-08-04T14:33:42.156Z</t>
   </si>
   <si>
     <t>TC-PERF-032</t>
@@ -2687,7 +2687,7 @@
     <t>Verify background tab CPU throttling resource conservation check</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:43.461Z</t>
+    <t>2026-08-04T14:33:42.173Z</t>
   </si>
   <si>
     <t>TC-PERF-033</t>
@@ -2696,7 +2696,7 @@
     <t>Verify camera frame buffer drop handler under heavy main thread load</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:43.490Z</t>
+    <t>2026-08-04T14:33:42.190Z</t>
   </si>
   <si>
     <t>TC-PERF-034</t>
@@ -2705,7 +2705,7 @@
     <t>Verify audio Web Audio API AudioContext resume latency on user touch (&lt;10ms)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:43.508Z</t>
+    <t>2026-08-04T14:33:42.211Z</t>
   </si>
   <si>
     <t>TC-PERF-035</t>
@@ -2714,7 +2714,7 @@
     <t>Verify session history 500-item virtualized list render initial time (&lt;150ms)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:43.523Z</t>
+    <t>2026-08-04T14:33:42.237Z</t>
   </si>
   <si>
     <t>TC-PERF-036</t>
@@ -2723,7 +2723,7 @@
     <t>Verify dark/light theme switch re-render duration (&lt;30ms)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:43.538Z</t>
+    <t>2026-08-04T14:33:42.253Z</t>
   </si>
   <si>
     <t>TC-PERF-037</t>
@@ -2732,7 +2732,7 @@
     <t>Verify responsive viewport resize debounced handler delay (&lt;50ms)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:43.558Z</t>
+    <t>2026-08-04T14:33:42.269Z</t>
   </si>
   <si>
     <t>TC-PERF-038</t>
@@ -2741,7 +2741,7 @@
     <t>Verify toast notification queue batching performance under rapid triggers</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:43.573Z</t>
+    <t>2026-08-04T14:33:42.287Z</t>
   </si>
   <si>
     <t>TC-PERF-039</t>
@@ -2750,7 +2750,7 @@
     <t>Verify form input validation debounced keyup handler (&lt;150ms delay)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:43.588Z</t>
+    <t>2026-08-04T14:33:42.302Z</t>
   </si>
   <si>
     <t>TC-PERF-040</t>
@@ -2759,7 +2759,7 @@
     <t>Verify achievement badge list rendering latency (&lt;40ms)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:43.605Z</t>
+    <t>2026-08-04T14:33:42.318Z</t>
   </si>
   <si>
     <t>TC-PERF-041</t>
@@ -2768,7 +2768,7 @@
     <t>Verify progress report 28-day streak grid render duration (&lt;35ms)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:43.620Z</t>
+    <t>2026-08-04T14:33:42.333Z</t>
   </si>
   <si>
     <t>TC-PERF-042</t>
@@ -2777,7 +2777,7 @@
     <t>Verify drawer menu slide animation frame consistency (60 FPS)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:43.644Z</t>
+    <t>2026-08-04T14:33:42.353Z</t>
   </si>
   <si>
     <t>TC-PERF-043</t>
@@ -2786,7 +2786,7 @@
     <t>Verify profile image base64 data URL decoding performance (&lt;20ms)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:43.659Z</t>
+    <t>2026-08-04T14:33:42.368Z</t>
   </si>
   <si>
     <t>TC-PERF-044</t>
@@ -2795,7 +2795,7 @@
     <t>Verify chart hover tooltip position calculation delay (&lt;5ms)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:43.676Z</t>
+    <t>2026-08-04T14:33:42.383Z</t>
   </si>
   <si>
     <t>TC-PERF-045</t>
@@ -2804,7 +2804,7 @@
     <t>Verify camera stream start to recording frame capture readiness (&lt;300ms)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:43.706Z</t>
+    <t>2026-08-04T14:33:42.398Z</t>
   </si>
   <si>
     <t>TC-PERF-046</t>
@@ -2813,7 +2813,7 @@
     <t>Verify camera recording stop to results screen transition time (&lt;500ms)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:43.722Z</t>
+    <t>2026-08-04T14:33:42.418Z</t>
   </si>
   <si>
     <t>TC-PERF-047</t>
@@ -2822,7 +2822,7 @@
     <t>Verify memory heap cleanup after navigating away from camera screen</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:43.741Z</t>
+    <t>2026-08-04T14:33:42.434Z</t>
   </si>
   <si>
     <t>TC-PERF-048</t>
@@ -2831,7 +2831,7 @@
     <t>Verify web worker message serialization overhead per pose payload (&lt;1ms)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:43.756Z</t>
+    <t>2026-08-04T14:33:42.458Z</t>
   </si>
   <si>
     <t>TC-PERF-049</t>
@@ -2840,7 +2840,7 @@
     <t>Verify session comparison modal delta calculation time (&lt;15ms)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:43.774Z</t>
+    <t>2026-08-04T14:33:42.483Z</t>
   </si>
   <si>
     <t>TC-PERF-050</t>
@@ -2849,7 +2849,7 @@
     <t>Verify web application initial cold start launch time (&lt;1.5s total)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:43.790Z</t>
+    <t>2026-08-04T14:33:42.507Z</t>
   </si>
 </sst>
 </file>
@@ -3494,7 +3494,7 @@
         <v>36</v>
       </c>
       <c r="F2">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="G2" t="s">
         <v>37</v>
@@ -3520,7 +3520,7 @@
         <v>36</v>
       </c>
       <c r="F3">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="G3" t="s">
         <v>41</v>
@@ -3546,7 +3546,7 @@
         <v>36</v>
       </c>
       <c r="F4">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="G4" t="s">
         <v>44</v>
@@ -3572,7 +3572,7 @@
         <v>36</v>
       </c>
       <c r="F5">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="G5" t="s">
         <v>47</v>
@@ -3598,7 +3598,7 @@
         <v>36</v>
       </c>
       <c r="F6">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="G6" t="s">
         <v>50</v>
@@ -3624,7 +3624,7 @@
         <v>36</v>
       </c>
       <c r="F7">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="G7" t="s">
         <v>53</v>
@@ -3650,7 +3650,7 @@
         <v>36</v>
       </c>
       <c r="F8">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G8" t="s">
         <v>56</v>
@@ -3676,7 +3676,7 @@
         <v>36</v>
       </c>
       <c r="F9">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="G9" t="s">
         <v>59</v>
@@ -3702,7 +3702,7 @@
         <v>36</v>
       </c>
       <c r="F10">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="G10" t="s">
         <v>62</v>
@@ -3728,7 +3728,7 @@
         <v>36</v>
       </c>
       <c r="F11">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G11" t="s">
         <v>65</v>
@@ -3754,7 +3754,7 @@
         <v>36</v>
       </c>
       <c r="F12">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="G12" t="s">
         <v>68</v>
@@ -3780,7 +3780,7 @@
         <v>36</v>
       </c>
       <c r="F13">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G13" t="s">
         <v>71</v>
@@ -3806,7 +3806,7 @@
         <v>36</v>
       </c>
       <c r="F14">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="G14" t="s">
         <v>74</v>
@@ -3832,7 +3832,7 @@
         <v>36</v>
       </c>
       <c r="F15">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G15" t="s">
         <v>77</v>
@@ -3858,7 +3858,7 @@
         <v>36</v>
       </c>
       <c r="F16">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G16" t="s">
         <v>80</v>
@@ -3884,7 +3884,7 @@
         <v>36</v>
       </c>
       <c r="F17">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G17" t="s">
         <v>83</v>
@@ -3910,7 +3910,7 @@
         <v>36</v>
       </c>
       <c r="F18">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="G18" t="s">
         <v>86</v>
@@ -3936,7 +3936,7 @@
         <v>36</v>
       </c>
       <c r="F19">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="G19" t="s">
         <v>89</v>
@@ -3988,7 +3988,7 @@
         <v>36</v>
       </c>
       <c r="F21">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="G21" t="s">
         <v>95</v>
@@ -4014,7 +4014,7 @@
         <v>36</v>
       </c>
       <c r="F22">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="G22" t="s">
         <v>98</v>
@@ -4066,7 +4066,7 @@
         <v>36</v>
       </c>
       <c r="F24">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="G24" t="s">
         <v>104</v>
@@ -4092,7 +4092,7 @@
         <v>36</v>
       </c>
       <c r="F25">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="G25" t="s">
         <v>107</v>
@@ -4118,7 +4118,7 @@
         <v>36</v>
       </c>
       <c r="F26">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G26" t="s">
         <v>110</v>
@@ -4144,7 +4144,7 @@
         <v>36</v>
       </c>
       <c r="F27">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G27" t="s">
         <v>113</v>
@@ -4170,7 +4170,7 @@
         <v>36</v>
       </c>
       <c r="F28">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="G28" t="s">
         <v>116</v>
@@ -4196,7 +4196,7 @@
         <v>36</v>
       </c>
       <c r="F29">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="G29" t="s">
         <v>119</v>
@@ -4222,7 +4222,7 @@
         <v>36</v>
       </c>
       <c r="F30">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G30" t="s">
         <v>122</v>
@@ -4248,7 +4248,7 @@
         <v>36</v>
       </c>
       <c r="F31">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="G31" t="s">
         <v>125</v>
@@ -4274,7 +4274,7 @@
         <v>36</v>
       </c>
       <c r="F32">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="G32" t="s">
         <v>128</v>
@@ -4300,7 +4300,7 @@
         <v>36</v>
       </c>
       <c r="F33">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G33" t="s">
         <v>131</v>
@@ -4326,7 +4326,7 @@
         <v>36</v>
       </c>
       <c r="F34">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G34" t="s">
         <v>134</v>
@@ -4352,7 +4352,7 @@
         <v>36</v>
       </c>
       <c r="F35">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="G35" t="s">
         <v>137</v>
@@ -4378,7 +4378,7 @@
         <v>36</v>
       </c>
       <c r="F36">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G36" t="s">
         <v>140</v>
@@ -4404,7 +4404,7 @@
         <v>36</v>
       </c>
       <c r="F37">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G37" t="s">
         <v>143</v>
@@ -4430,7 +4430,7 @@
         <v>36</v>
       </c>
       <c r="F38">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="G38" t="s">
         <v>146</v>
@@ -4456,7 +4456,7 @@
         <v>36</v>
       </c>
       <c r="F39">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G39" t="s">
         <v>149</v>
@@ -4482,7 +4482,7 @@
         <v>36</v>
       </c>
       <c r="F40">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="G40" t="s">
         <v>152</v>
@@ -4508,7 +4508,7 @@
         <v>36</v>
       </c>
       <c r="F41">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G41" t="s">
         <v>155</v>
@@ -4534,7 +4534,7 @@
         <v>36</v>
       </c>
       <c r="F42">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G42" t="s">
         <v>158</v>
@@ -4560,7 +4560,7 @@
         <v>36</v>
       </c>
       <c r="F43">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G43" t="s">
         <v>161</v>
@@ -4586,7 +4586,7 @@
         <v>36</v>
       </c>
       <c r="F44">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G44" t="s">
         <v>164</v>
@@ -4638,7 +4638,7 @@
         <v>36</v>
       </c>
       <c r="F46">
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="G46" t="s">
         <v>170</v>
@@ -4690,7 +4690,7 @@
         <v>36</v>
       </c>
       <c r="F48">
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="G48" t="s">
         <v>176</v>
@@ -4716,7 +4716,7 @@
         <v>36</v>
       </c>
       <c r="F49">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G49" t="s">
         <v>179</v>
@@ -4742,7 +4742,7 @@
         <v>36</v>
       </c>
       <c r="F50">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G50" t="s">
         <v>182</v>
@@ -4768,7 +4768,7 @@
         <v>36</v>
       </c>
       <c r="F51">
-        <v>75</v>
+        <v>41</v>
       </c>
       <c r="G51" t="s">
         <v>185</v>
@@ -4794,7 +4794,7 @@
         <v>36</v>
       </c>
       <c r="F52">
-        <v>17278</v>
+        <v>1794</v>
       </c>
       <c r="G52" t="s">
         <v>190</v>
@@ -4820,7 +4820,7 @@
         <v>36</v>
       </c>
       <c r="F53">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="G53" t="s">
         <v>193</v>
@@ -4846,7 +4846,7 @@
         <v>36</v>
       </c>
       <c r="F54">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="G54" t="s">
         <v>196</v>
@@ -4872,7 +4872,7 @@
         <v>36</v>
       </c>
       <c r="F55">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G55" t="s">
         <v>199</v>
@@ -4898,7 +4898,7 @@
         <v>36</v>
       </c>
       <c r="F56">
-        <v>250</v>
+        <v>63</v>
       </c>
       <c r="G56" t="s">
         <v>202</v>
@@ -4924,7 +4924,7 @@
         <v>36</v>
       </c>
       <c r="F57">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="G57" t="s">
         <v>205</v>
@@ -4950,7 +4950,7 @@
         <v>36</v>
       </c>
       <c r="F58">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="G58" t="s">
         <v>208</v>
@@ -4976,7 +4976,7 @@
         <v>36</v>
       </c>
       <c r="F59">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="G59" t="s">
         <v>211</v>
@@ -5002,7 +5002,7 @@
         <v>36</v>
       </c>
       <c r="F60">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="G60" t="s">
         <v>214</v>
@@ -5028,7 +5028,7 @@
         <v>36</v>
       </c>
       <c r="F61">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="G61" t="s">
         <v>217</v>
@@ -5054,7 +5054,7 @@
         <v>36</v>
       </c>
       <c r="F62">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="G62" t="s">
         <v>220</v>
@@ -5080,7 +5080,7 @@
         <v>36</v>
       </c>
       <c r="F63">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G63" t="s">
         <v>223</v>
@@ -5106,7 +5106,7 @@
         <v>36</v>
       </c>
       <c r="F64">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G64" t="s">
         <v>226</v>
@@ -5132,7 +5132,7 @@
         <v>36</v>
       </c>
       <c r="F65">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G65" t="s">
         <v>229</v>
@@ -5158,7 +5158,7 @@
         <v>36</v>
       </c>
       <c r="F66">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G66" t="s">
         <v>232</v>
@@ -5184,7 +5184,7 @@
         <v>36</v>
       </c>
       <c r="F67">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G67" t="s">
         <v>235</v>
@@ -5210,7 +5210,7 @@
         <v>36</v>
       </c>
       <c r="F68">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G68" t="s">
         <v>238</v>
@@ -5236,7 +5236,7 @@
         <v>36</v>
       </c>
       <c r="F69">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G69" t="s">
         <v>241</v>
@@ -5262,7 +5262,7 @@
         <v>36</v>
       </c>
       <c r="F70">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="G70" t="s">
         <v>244</v>
@@ -5288,7 +5288,7 @@
         <v>36</v>
       </c>
       <c r="F71">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="G71" t="s">
         <v>247</v>
@@ -5314,7 +5314,7 @@
         <v>36</v>
       </c>
       <c r="F72">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="G72" t="s">
         <v>250</v>
@@ -5340,7 +5340,7 @@
         <v>36</v>
       </c>
       <c r="F73">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="G73" t="s">
         <v>253</v>
@@ -5366,7 +5366,7 @@
         <v>36</v>
       </c>
       <c r="F74">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="G74" t="s">
         <v>256</v>
@@ -5392,7 +5392,7 @@
         <v>36</v>
       </c>
       <c r="F75">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="G75" t="s">
         <v>259</v>
@@ -5418,7 +5418,7 @@
         <v>36</v>
       </c>
       <c r="F76">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="G76" t="s">
         <v>262</v>
@@ -5444,7 +5444,7 @@
         <v>36</v>
       </c>
       <c r="F77">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="G77" t="s">
         <v>265</v>
@@ -5470,7 +5470,7 @@
         <v>36</v>
       </c>
       <c r="F78">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="G78" t="s">
         <v>268</v>
@@ -5496,7 +5496,7 @@
         <v>36</v>
       </c>
       <c r="F79">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="G79" t="s">
         <v>271</v>
@@ -5522,7 +5522,7 @@
         <v>36</v>
       </c>
       <c r="F80">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="G80" t="s">
         <v>274</v>
@@ -5548,7 +5548,7 @@
         <v>36</v>
       </c>
       <c r="F81">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G81" t="s">
         <v>277</v>
@@ -5574,7 +5574,7 @@
         <v>36</v>
       </c>
       <c r="F82">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G82" t="s">
         <v>280</v>
@@ -5600,7 +5600,7 @@
         <v>36</v>
       </c>
       <c r="F83">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="G83" t="s">
         <v>283</v>
@@ -5626,7 +5626,7 @@
         <v>36</v>
       </c>
       <c r="F84">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="G84" t="s">
         <v>286</v>
@@ -5652,7 +5652,7 @@
         <v>36</v>
       </c>
       <c r="F85">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G85" t="s">
         <v>289</v>
@@ -5730,7 +5730,7 @@
         <v>36</v>
       </c>
       <c r="F88">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G88" t="s">
         <v>298</v>
@@ -5756,7 +5756,7 @@
         <v>36</v>
       </c>
       <c r="F89">
-        <v>105</v>
+        <v>63</v>
       </c>
       <c r="G89" t="s">
         <v>301</v>
@@ -5808,7 +5808,7 @@
         <v>36</v>
       </c>
       <c r="F91">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="G91" t="s">
         <v>307</v>
@@ -5834,7 +5834,7 @@
         <v>36</v>
       </c>
       <c r="F92">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="G92" t="s">
         <v>310</v>
@@ -5860,7 +5860,7 @@
         <v>36</v>
       </c>
       <c r="F93">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="G93" t="s">
         <v>313</v>
@@ -5886,7 +5886,7 @@
         <v>36</v>
       </c>
       <c r="F94">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G94" t="s">
         <v>316</v>
@@ -5912,7 +5912,7 @@
         <v>36</v>
       </c>
       <c r="F95">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="G95" t="s">
         <v>319</v>
@@ -5938,7 +5938,7 @@
         <v>36</v>
       </c>
       <c r="F96">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="G96" t="s">
         <v>322</v>
@@ -5964,7 +5964,7 @@
         <v>36</v>
       </c>
       <c r="F97">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G97" t="s">
         <v>325</v>
@@ -5990,7 +5990,7 @@
         <v>36</v>
       </c>
       <c r="F98">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G98" t="s">
         <v>328</v>
@@ -6016,7 +6016,7 @@
         <v>36</v>
       </c>
       <c r="F99">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="G99" t="s">
         <v>331</v>
@@ -6042,7 +6042,7 @@
         <v>36</v>
       </c>
       <c r="F100">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="G100" t="s">
         <v>334</v>
@@ -6068,7 +6068,7 @@
         <v>36</v>
       </c>
       <c r="F101">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G101" t="s">
         <v>337</v>
@@ -6146,7 +6146,7 @@
         <v>36</v>
       </c>
       <c r="F104">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="G104" t="s">
         <v>346</v>
@@ -6172,7 +6172,7 @@
         <v>36</v>
       </c>
       <c r="F105">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="G105" t="s">
         <v>349</v>
@@ -6198,7 +6198,7 @@
         <v>36</v>
       </c>
       <c r="F106">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="G106" t="s">
         <v>352</v>
@@ -6224,7 +6224,7 @@
         <v>36</v>
       </c>
       <c r="F107">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="G107" t="s">
         <v>355</v>
@@ -6250,7 +6250,7 @@
         <v>36</v>
       </c>
       <c r="F108">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G108" t="s">
         <v>358</v>
@@ -6276,7 +6276,7 @@
         <v>36</v>
       </c>
       <c r="F109">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="G109" t="s">
         <v>361</v>
@@ -6302,7 +6302,7 @@
         <v>36</v>
       </c>
       <c r="F110">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="G110" t="s">
         <v>364</v>
@@ -6328,7 +6328,7 @@
         <v>36</v>
       </c>
       <c r="F111">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="G111" t="s">
         <v>367</v>
@@ -6354,7 +6354,7 @@
         <v>36</v>
       </c>
       <c r="F112">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G112" t="s">
         <v>372</v>
@@ -6380,7 +6380,7 @@
         <v>36</v>
       </c>
       <c r="F113">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="G113" t="s">
         <v>375</v>
@@ -6406,7 +6406,7 @@
         <v>36</v>
       </c>
       <c r="F114">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G114" t="s">
         <v>378</v>
@@ -6432,7 +6432,7 @@
         <v>36</v>
       </c>
       <c r="F115">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="G115" t="s">
         <v>381</v>
@@ -6458,7 +6458,7 @@
         <v>36</v>
       </c>
       <c r="F116">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="G116" t="s">
         <v>384</v>
@@ -6484,7 +6484,7 @@
         <v>36</v>
       </c>
       <c r="F117">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G117" t="s">
         <v>387</v>
@@ -6510,7 +6510,7 @@
         <v>36</v>
       </c>
       <c r="F118">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="G118" t="s">
         <v>390</v>
@@ -6536,7 +6536,7 @@
         <v>36</v>
       </c>
       <c r="F119">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="G119" t="s">
         <v>393</v>
@@ -6562,7 +6562,7 @@
         <v>36</v>
       </c>
       <c r="F120">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="G120" t="s">
         <v>396</v>
@@ -6588,7 +6588,7 @@
         <v>36</v>
       </c>
       <c r="F121">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="G121" t="s">
         <v>399</v>
@@ -6614,7 +6614,7 @@
         <v>36</v>
       </c>
       <c r="F122">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="G122" t="s">
         <v>402</v>
@@ -6640,7 +6640,7 @@
         <v>36</v>
       </c>
       <c r="F123">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="G123" t="s">
         <v>405</v>
@@ -6666,7 +6666,7 @@
         <v>36</v>
       </c>
       <c r="F124">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="G124" t="s">
         <v>408</v>
@@ -6692,7 +6692,7 @@
         <v>36</v>
       </c>
       <c r="F125">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="G125" t="s">
         <v>411</v>
@@ -6718,7 +6718,7 @@
         <v>36</v>
       </c>
       <c r="F126">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G126" t="s">
         <v>414</v>
@@ -6744,7 +6744,7 @@
         <v>36</v>
       </c>
       <c r="F127">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="G127" t="s">
         <v>417</v>
@@ -6770,7 +6770,7 @@
         <v>36</v>
       </c>
       <c r="F128">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G128" t="s">
         <v>420</v>
@@ -6796,7 +6796,7 @@
         <v>36</v>
       </c>
       <c r="F129">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G129" t="s">
         <v>423</v>
@@ -6822,7 +6822,7 @@
         <v>36</v>
       </c>
       <c r="F130">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="G130" t="s">
         <v>426</v>
@@ -6848,7 +6848,7 @@
         <v>36</v>
       </c>
       <c r="F131">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G131" t="s">
         <v>429</v>
@@ -6874,7 +6874,7 @@
         <v>36</v>
       </c>
       <c r="F132">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="G132" t="s">
         <v>432</v>
@@ -6900,7 +6900,7 @@
         <v>36</v>
       </c>
       <c r="F133">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="G133" t="s">
         <v>435</v>
@@ -6926,7 +6926,7 @@
         <v>36</v>
       </c>
       <c r="F134">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="G134" t="s">
         <v>438</v>
@@ -6952,7 +6952,7 @@
         <v>36</v>
       </c>
       <c r="F135">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="G135" t="s">
         <v>441</v>
@@ -6978,7 +6978,7 @@
         <v>36</v>
       </c>
       <c r="F136">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="G136" t="s">
         <v>444</v>
@@ -7030,7 +7030,7 @@
         <v>36</v>
       </c>
       <c r="F138">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G138" t="s">
         <v>450</v>
@@ -7056,7 +7056,7 @@
         <v>36</v>
       </c>
       <c r="F139">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="G139" t="s">
         <v>453</v>
@@ -7082,7 +7082,7 @@
         <v>36</v>
       </c>
       <c r="F140">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G140" t="s">
         <v>456</v>
@@ -7108,7 +7108,7 @@
         <v>36</v>
       </c>
       <c r="F141">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="G141" t="s">
         <v>459</v>
@@ -7134,7 +7134,7 @@
         <v>36</v>
       </c>
       <c r="F142">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="G142" t="s">
         <v>462</v>
@@ -7186,7 +7186,7 @@
         <v>36</v>
       </c>
       <c r="F144">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G144" t="s">
         <v>468</v>
@@ -7212,7 +7212,7 @@
         <v>36</v>
       </c>
       <c r="F145">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G145" t="s">
         <v>471</v>
@@ -7238,7 +7238,7 @@
         <v>36</v>
       </c>
       <c r="F146">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G146" t="s">
         <v>474</v>
@@ -7264,7 +7264,7 @@
         <v>36</v>
       </c>
       <c r="F147">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G147" t="s">
         <v>477</v>
@@ -7290,7 +7290,7 @@
         <v>36</v>
       </c>
       <c r="F148">
-        <v>50</v>
+        <v>88</v>
       </c>
       <c r="G148" t="s">
         <v>480</v>
@@ -7316,7 +7316,7 @@
         <v>36</v>
       </c>
       <c r="F149">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="G149" t="s">
         <v>483</v>
@@ -7342,7 +7342,7 @@
         <v>36</v>
       </c>
       <c r="F150">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="G150" t="s">
         <v>486</v>
@@ -7368,7 +7368,7 @@
         <v>36</v>
       </c>
       <c r="F151">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G151" t="s">
         <v>489</v>
@@ -7394,7 +7394,7 @@
         <v>36</v>
       </c>
       <c r="F152">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="G152" t="s">
         <v>492</v>
@@ -7420,7 +7420,7 @@
         <v>36</v>
       </c>
       <c r="F153">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="G153" t="s">
         <v>495</v>
@@ -7446,7 +7446,7 @@
         <v>36</v>
       </c>
       <c r="F154">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="G154" t="s">
         <v>498</v>
@@ -7472,7 +7472,7 @@
         <v>36</v>
       </c>
       <c r="F155">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G155" t="s">
         <v>501</v>
@@ -7498,7 +7498,7 @@
         <v>36</v>
       </c>
       <c r="F156">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="G156" t="s">
         <v>504</v>
@@ -7524,7 +7524,7 @@
         <v>36</v>
       </c>
       <c r="F157">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G157" t="s">
         <v>507</v>
@@ -7550,7 +7550,7 @@
         <v>36</v>
       </c>
       <c r="F158">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G158" t="s">
         <v>510</v>
@@ -7576,7 +7576,7 @@
         <v>36</v>
       </c>
       <c r="F159">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="G159" t="s">
         <v>513</v>
@@ -7602,7 +7602,7 @@
         <v>36</v>
       </c>
       <c r="F160">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="G160" t="s">
         <v>516</v>
@@ -7628,7 +7628,7 @@
         <v>36</v>
       </c>
       <c r="F161">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="G161" t="s">
         <v>519</v>
@@ -7654,7 +7654,7 @@
         <v>36</v>
       </c>
       <c r="F162">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="G162" t="s">
         <v>524</v>
@@ -7706,7 +7706,7 @@
         <v>36</v>
       </c>
       <c r="F164">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="G164" t="s">
         <v>530</v>
@@ -7732,7 +7732,7 @@
         <v>36</v>
       </c>
       <c r="F165">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="G165" t="s">
         <v>533</v>
@@ -7758,7 +7758,7 @@
         <v>36</v>
       </c>
       <c r="F166">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G166" t="s">
         <v>536</v>
@@ -7784,7 +7784,7 @@
         <v>36</v>
       </c>
       <c r="F167">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G167" t="s">
         <v>539</v>
@@ -7810,7 +7810,7 @@
         <v>36</v>
       </c>
       <c r="F168">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="G168" t="s">
         <v>542</v>
@@ -7836,7 +7836,7 @@
         <v>36</v>
       </c>
       <c r="F169">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G169" t="s">
         <v>545</v>
@@ -7862,7 +7862,7 @@
         <v>36</v>
       </c>
       <c r="F170">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G170" t="s">
         <v>548</v>
@@ -7888,7 +7888,7 @@
         <v>36</v>
       </c>
       <c r="F171">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="G171" t="s">
         <v>551</v>
@@ -7914,7 +7914,7 @@
         <v>36</v>
       </c>
       <c r="F172">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G172" t="s">
         <v>554</v>
@@ -7940,7 +7940,7 @@
         <v>36</v>
       </c>
       <c r="F173">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G173" t="s">
         <v>557</v>
@@ -7966,7 +7966,7 @@
         <v>36</v>
       </c>
       <c r="F174">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G174" t="s">
         <v>560</v>
@@ -7992,7 +7992,7 @@
         <v>36</v>
       </c>
       <c r="F175">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="G175" t="s">
         <v>563</v>
@@ -8018,7 +8018,7 @@
         <v>36</v>
       </c>
       <c r="F176">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="G176" t="s">
         <v>566</v>
@@ -8044,7 +8044,7 @@
         <v>36</v>
       </c>
       <c r="F177">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="G177" t="s">
         <v>569</v>
@@ -8070,7 +8070,7 @@
         <v>36</v>
       </c>
       <c r="F178">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G178" t="s">
         <v>572</v>
@@ -8122,7 +8122,7 @@
         <v>36</v>
       </c>
       <c r="F180">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="G180" t="s">
         <v>578</v>
@@ -8148,7 +8148,7 @@
         <v>36</v>
       </c>
       <c r="F181">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="G181" t="s">
         <v>581</v>
@@ -8174,7 +8174,7 @@
         <v>36</v>
       </c>
       <c r="F182">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="G182" t="s">
         <v>584</v>
@@ -8200,7 +8200,7 @@
         <v>36</v>
       </c>
       <c r="F183">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G183" t="s">
         <v>587</v>
@@ -8226,7 +8226,7 @@
         <v>36</v>
       </c>
       <c r="F184">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="G184" t="s">
         <v>590</v>
@@ -8252,7 +8252,7 @@
         <v>36</v>
       </c>
       <c r="F185">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G185" t="s">
         <v>593</v>
@@ -8278,7 +8278,7 @@
         <v>36</v>
       </c>
       <c r="F186">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="G186" t="s">
         <v>596</v>
@@ -8304,7 +8304,7 @@
         <v>36</v>
       </c>
       <c r="F187">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="G187" t="s">
         <v>599</v>
@@ -8330,7 +8330,7 @@
         <v>36</v>
       </c>
       <c r="F188">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="G188" t="s">
         <v>602</v>
@@ -8382,7 +8382,7 @@
         <v>36</v>
       </c>
       <c r="F190">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G190" t="s">
         <v>608</v>
@@ -8408,7 +8408,7 @@
         <v>36</v>
       </c>
       <c r="F191">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="G191" t="s">
         <v>611</v>
@@ -8434,7 +8434,7 @@
         <v>36</v>
       </c>
       <c r="F192">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G192" t="s">
         <v>614</v>
@@ -8460,7 +8460,7 @@
         <v>36</v>
       </c>
       <c r="F193">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="G193" t="s">
         <v>617</v>
@@ -8486,7 +8486,7 @@
         <v>36</v>
       </c>
       <c r="F194">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G194" t="s">
         <v>620</v>
@@ -8538,7 +8538,7 @@
         <v>36</v>
       </c>
       <c r="F196">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="G196" t="s">
         <v>626</v>
@@ -8564,7 +8564,7 @@
         <v>36</v>
       </c>
       <c r="F197">
-        <v>38</v>
+        <v>117</v>
       </c>
       <c r="G197" t="s">
         <v>629</v>
@@ -8590,7 +8590,7 @@
         <v>36</v>
       </c>
       <c r="F198">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G198" t="s">
         <v>632</v>
@@ -8616,7 +8616,7 @@
         <v>36</v>
       </c>
       <c r="F199">
-        <v>37</v>
+        <v>317</v>
       </c>
       <c r="G199" t="s">
         <v>635</v>
@@ -8642,7 +8642,7 @@
         <v>36</v>
       </c>
       <c r="F200">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="G200" t="s">
         <v>638</v>
@@ -8668,7 +8668,7 @@
         <v>36</v>
       </c>
       <c r="F201">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="G201" t="s">
         <v>641</v>
@@ -8694,7 +8694,7 @@
         <v>36</v>
       </c>
       <c r="F202">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G202" t="s">
         <v>644</v>
@@ -8720,7 +8720,7 @@
         <v>36</v>
       </c>
       <c r="F203">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G203" t="s">
         <v>647</v>
@@ -8772,7 +8772,7 @@
         <v>36</v>
       </c>
       <c r="F205">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G205" t="s">
         <v>653</v>
@@ -8798,7 +8798,7 @@
         <v>36</v>
       </c>
       <c r="F206">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G206" t="s">
         <v>656</v>
@@ -8824,7 +8824,7 @@
         <v>36</v>
       </c>
       <c r="F207">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G207" t="s">
         <v>659</v>
@@ -8850,7 +8850,7 @@
         <v>36</v>
       </c>
       <c r="F208">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="G208" t="s">
         <v>662</v>
@@ -8902,7 +8902,7 @@
         <v>36</v>
       </c>
       <c r="F210">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G210" t="s">
         <v>668</v>
@@ -8928,7 +8928,7 @@
         <v>36</v>
       </c>
       <c r="F211">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G211" t="s">
         <v>671</v>
@@ -8954,7 +8954,7 @@
         <v>36</v>
       </c>
       <c r="F212">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G212" t="s">
         <v>676</v>
@@ -9006,7 +9006,7 @@
         <v>36</v>
       </c>
       <c r="F214">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G214" t="s">
         <v>682</v>
@@ -9032,7 +9032,7 @@
         <v>36</v>
       </c>
       <c r="F215">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="G215" t="s">
         <v>685</v>
@@ -9058,7 +9058,7 @@
         <v>36</v>
       </c>
       <c r="F216">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="G216" t="s">
         <v>688</v>
@@ -9084,7 +9084,7 @@
         <v>36</v>
       </c>
       <c r="F217">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G217" t="s">
         <v>691</v>
@@ -9110,7 +9110,7 @@
         <v>36</v>
       </c>
       <c r="F218">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G218" t="s">
         <v>694</v>
@@ -9136,7 +9136,7 @@
         <v>36</v>
       </c>
       <c r="F219">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G219" t="s">
         <v>697</v>
@@ -9162,7 +9162,7 @@
         <v>36</v>
       </c>
       <c r="F220">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G220" t="s">
         <v>700</v>
@@ -9188,7 +9188,7 @@
         <v>36</v>
       </c>
       <c r="F221">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G221" t="s">
         <v>703</v>
@@ -9214,7 +9214,7 @@
         <v>36</v>
       </c>
       <c r="F222">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G222" t="s">
         <v>706</v>
@@ -9240,7 +9240,7 @@
         <v>36</v>
       </c>
       <c r="F223">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G223" t="s">
         <v>709</v>
@@ -9266,7 +9266,7 @@
         <v>36</v>
       </c>
       <c r="F224">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="G224" t="s">
         <v>712</v>
@@ -9292,7 +9292,7 @@
         <v>36</v>
       </c>
       <c r="F225">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G225" t="s">
         <v>715</v>
@@ -9318,7 +9318,7 @@
         <v>36</v>
       </c>
       <c r="F226">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G226" t="s">
         <v>718</v>
@@ -9344,7 +9344,7 @@
         <v>36</v>
       </c>
       <c r="F227">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G227" t="s">
         <v>721</v>
@@ -9370,7 +9370,7 @@
         <v>36</v>
       </c>
       <c r="F228">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="G228" t="s">
         <v>724</v>
@@ -9396,7 +9396,7 @@
         <v>36</v>
       </c>
       <c r="F229">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="G229" t="s">
         <v>727</v>
@@ -9448,7 +9448,7 @@
         <v>36</v>
       </c>
       <c r="F231">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="G231" t="s">
         <v>733</v>
@@ -9474,7 +9474,7 @@
         <v>36</v>
       </c>
       <c r="F232">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="G232" t="s">
         <v>736</v>
@@ -9500,7 +9500,7 @@
         <v>36</v>
       </c>
       <c r="F233">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G233" t="s">
         <v>739</v>
@@ -9526,7 +9526,7 @@
         <v>36</v>
       </c>
       <c r="F234">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G234" t="s">
         <v>742</v>
@@ -9552,7 +9552,7 @@
         <v>36</v>
       </c>
       <c r="F235">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="G235" t="s">
         <v>745</v>
@@ -9604,7 +9604,7 @@
         <v>36</v>
       </c>
       <c r="F237">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="G237" t="s">
         <v>751</v>
@@ -9630,7 +9630,7 @@
         <v>36</v>
       </c>
       <c r="F238">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G238" t="s">
         <v>754</v>
@@ -9656,7 +9656,7 @@
         <v>36</v>
       </c>
       <c r="F239">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G239" t="s">
         <v>757</v>
@@ -9682,7 +9682,7 @@
         <v>36</v>
       </c>
       <c r="F240">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="G240" t="s">
         <v>760</v>
@@ -9708,7 +9708,7 @@
         <v>36</v>
       </c>
       <c r="F241">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="G241" t="s">
         <v>763</v>
@@ -9734,7 +9734,7 @@
         <v>36</v>
       </c>
       <c r="F242">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="G242" t="s">
         <v>766</v>
@@ -9760,7 +9760,7 @@
         <v>36</v>
       </c>
       <c r="F243">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="G243" t="s">
         <v>769</v>
@@ -9786,7 +9786,7 @@
         <v>36</v>
       </c>
       <c r="F244">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="G244" t="s">
         <v>772</v>
@@ -9812,7 +9812,7 @@
         <v>36</v>
       </c>
       <c r="F245">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="G245" t="s">
         <v>775</v>
@@ -9838,7 +9838,7 @@
         <v>36</v>
       </c>
       <c r="F246">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="G246" t="s">
         <v>778</v>
@@ -9890,7 +9890,7 @@
         <v>36</v>
       </c>
       <c r="F248">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="G248" t="s">
         <v>784</v>
@@ -9916,7 +9916,7 @@
         <v>36</v>
       </c>
       <c r="F249">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="G249" t="s">
         <v>787</v>
@@ -9942,7 +9942,7 @@
         <v>36</v>
       </c>
       <c r="F250">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="G250" t="s">
         <v>790</v>
@@ -9968,7 +9968,7 @@
         <v>36</v>
       </c>
       <c r="F251">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="G251" t="s">
         <v>793</v>
@@ -10020,7 +10020,7 @@
         <v>36</v>
       </c>
       <c r="F253">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G253" t="s">
         <v>801</v>
@@ -10046,7 +10046,7 @@
         <v>36</v>
       </c>
       <c r="F254">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="G254" t="s">
         <v>804</v>
@@ -10072,7 +10072,7 @@
         <v>36</v>
       </c>
       <c r="F255">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="G255" t="s">
         <v>807</v>
@@ -10098,7 +10098,7 @@
         <v>36</v>
       </c>
       <c r="F256">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="G256" t="s">
         <v>810</v>
@@ -10124,7 +10124,7 @@
         <v>36</v>
       </c>
       <c r="F257">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="G257" t="s">
         <v>813</v>
@@ -10150,7 +10150,7 @@
         <v>36</v>
       </c>
       <c r="F258">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="G258" t="s">
         <v>816</v>
@@ -10176,7 +10176,7 @@
         <v>36</v>
       </c>
       <c r="F259">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G259" t="s">
         <v>819</v>
@@ -10202,7 +10202,7 @@
         <v>36</v>
       </c>
       <c r="F260">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G260" t="s">
         <v>822</v>
@@ -10228,7 +10228,7 @@
         <v>36</v>
       </c>
       <c r="F261">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="G261" t="s">
         <v>825</v>
@@ -10254,7 +10254,7 @@
         <v>36</v>
       </c>
       <c r="F262">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G262" t="s">
         <v>828</v>
@@ -10280,7 +10280,7 @@
         <v>36</v>
       </c>
       <c r="F263">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G263" t="s">
         <v>831</v>
@@ -10306,7 +10306,7 @@
         <v>36</v>
       </c>
       <c r="F264">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G264" t="s">
         <v>834</v>
@@ -10332,7 +10332,7 @@
         <v>36</v>
       </c>
       <c r="F265">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G265" t="s">
         <v>837</v>
@@ -10358,7 +10358,7 @@
         <v>36</v>
       </c>
       <c r="F266">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="G266" t="s">
         <v>840</v>
@@ -10384,7 +10384,7 @@
         <v>36</v>
       </c>
       <c r="F267">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G267" t="s">
         <v>843</v>
@@ -10410,7 +10410,7 @@
         <v>36</v>
       </c>
       <c r="F268">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="G268" t="s">
         <v>846</v>
@@ -10436,7 +10436,7 @@
         <v>36</v>
       </c>
       <c r="F269">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="G269" t="s">
         <v>849</v>
@@ -10462,7 +10462,7 @@
         <v>36</v>
       </c>
       <c r="F270">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G270" t="s">
         <v>852</v>
@@ -10488,7 +10488,7 @@
         <v>36</v>
       </c>
       <c r="F271">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="G271" t="s">
         <v>855</v>
@@ -10514,7 +10514,7 @@
         <v>36</v>
       </c>
       <c r="F272">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G272" t="s">
         <v>858</v>
@@ -10540,7 +10540,7 @@
         <v>36</v>
       </c>
       <c r="F273">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="G273" t="s">
         <v>861</v>
@@ -10566,7 +10566,7 @@
         <v>36</v>
       </c>
       <c r="F274">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="G274" t="s">
         <v>864</v>
@@ -10618,7 +10618,7 @@
         <v>36</v>
       </c>
       <c r="F276">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="G276" t="s">
         <v>870</v>
@@ -10644,7 +10644,7 @@
         <v>36</v>
       </c>
       <c r="F277">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="G277" t="s">
         <v>873</v>
@@ -10670,7 +10670,7 @@
         <v>36</v>
       </c>
       <c r="F278">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G278" t="s">
         <v>876</v>
@@ -10696,7 +10696,7 @@
         <v>36</v>
       </c>
       <c r="F279">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G279" t="s">
         <v>879</v>
@@ -10722,7 +10722,7 @@
         <v>36</v>
       </c>
       <c r="F280">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G280" t="s">
         <v>882</v>
@@ -10748,7 +10748,7 @@
         <v>36</v>
       </c>
       <c r="F281">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G281" t="s">
         <v>885</v>
@@ -10774,7 +10774,7 @@
         <v>36</v>
       </c>
       <c r="F282">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="G282" t="s">
         <v>888</v>
@@ -10800,7 +10800,7 @@
         <v>36</v>
       </c>
       <c r="F283">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G283" t="s">
         <v>891</v>
@@ -10826,7 +10826,7 @@
         <v>36</v>
       </c>
       <c r="F284">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="G284" t="s">
         <v>894</v>
@@ -10852,7 +10852,7 @@
         <v>36</v>
       </c>
       <c r="F285">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="G285" t="s">
         <v>897</v>
@@ -10878,7 +10878,7 @@
         <v>36</v>
       </c>
       <c r="F286">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="G286" t="s">
         <v>900</v>
@@ -10904,7 +10904,7 @@
         <v>36</v>
       </c>
       <c r="F287">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G287" t="s">
         <v>903</v>
@@ -10930,7 +10930,7 @@
         <v>36</v>
       </c>
       <c r="F288">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="G288" t="s">
         <v>906</v>
@@ -10956,7 +10956,7 @@
         <v>36</v>
       </c>
       <c r="F289">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G289" t="s">
         <v>909</v>
@@ -11060,7 +11060,7 @@
         <v>36</v>
       </c>
       <c r="F293">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G293" t="s">
         <v>921</v>
@@ -11112,7 +11112,7 @@
         <v>36</v>
       </c>
       <c r="F295">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G295" t="s">
         <v>927</v>
@@ -11138,7 +11138,7 @@
         <v>36</v>
       </c>
       <c r="F296">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="G296" t="s">
         <v>930</v>
@@ -11164,7 +11164,7 @@
         <v>36</v>
       </c>
       <c r="F297">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="G297" t="s">
         <v>933</v>
@@ -11190,7 +11190,7 @@
         <v>36</v>
       </c>
       <c r="F298">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="G298" t="s">
         <v>936</v>
@@ -11216,7 +11216,7 @@
         <v>36</v>
       </c>
       <c r="F299">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="G299" t="s">
         <v>939</v>
@@ -11242,7 +11242,7 @@
         <v>36</v>
       </c>
       <c r="F300">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="G300" t="s">
         <v>942</v>
@@ -11268,7 +11268,7 @@
         <v>36</v>
       </c>
       <c r="F301">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="G301" t="s">
         <v>945</v>
